--- a/workspaces/btc_daily_14days/drawdown/drawdown_90.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_90.xlsx
@@ -575,46 +575,46 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.68837986160614</v>
+        <v>15.63737772255789</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.106033362766482</v>
+        <v>-4.092754778058932</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.502092765146564</v>
+        <v>-4.487713950206306</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.72481821792617</v>
+        <v>4.709492803147171</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.187089438288183</v>
+        <v>4.173344962042336</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.037063834153891</v>
+        <v>9.007665680144775</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.40221142667491</v>
+        <v>4.387818611969521</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.488886302627087</v>
+        <v>8.46094267849994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.429712704479229</v>
+        <v>8.402294315311742</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>16.69140713510123</v>
+        <v>16.63683114232944</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>21.04705707159656</v>
+        <v>20.97850534813506</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.52862195865269</v>
+        <v>16.47500479394618</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.55204206285953</v>
+        <v>11.51466962955441</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.8054159141236</v>
+        <v>11.76726576439357</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>37</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.560615733842852</v>
+        <v>1.555232738093281</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.0509705212145235</v>
+        <v>-0.05080617399298148</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.150091543329552</v>
+        <v>-3.139936886417068</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.50320424933343</v>
+        <v>10.46868105226071</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.261510994725953</v>
+        <v>7.237468941628286</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.855047796586746</v>
+        <v>4.838940480303265</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6421876675436238</v>
+        <v>-0.6402350246329931</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.817655792286779</v>
+        <v>-3.80561548373803</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.879916129072406</v>
+        <v>-3.867332626860623</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.102794475407023</v>
+        <v>6.082165952587374</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.31811498581617</v>
+        <v>11.28048035715968</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.644991064423749</v>
+        <v>8.616455664596302</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.225522363034294</v>
+        <v>8.198513511175499</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.766503580957902</v>
+        <v>5.747609744737559</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.97167795886191</v>
+        <v>7.944907562399401</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.01407911494017</v>
+        <v>10.97752339642548</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.62183614317013</v>
+        <v>10.5864910075444</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.100246186169151</v>
+        <v>6.079630724367597</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.21879894041271</v>
+        <v>10.18445101354891</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15.17633171132906</v>
+        <v>15.12564045933271</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.43698985456748</v>
+        <v>10.40221206695468</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.98254784884945</v>
+        <v>2.97226509826023</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>14.57370552063211</v>
+        <v>14.5253009193816</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.39494410577561</v>
+        <v>11.35633033224683</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>13.52421265216691</v>
+        <v>13.47848763802199</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.89399978035253</v>
+        <v>15.84082308736939</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>17.80913138806502</v>
+        <v>17.74976419424463</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>15.73082079682216</v>
+        <v>15.67847083839041</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>39</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-8.903694730467549</v>
+        <v>-8.874460827689731</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-10.51794925991248</v>
+        <v>-10.48309734563932</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-16.04654316184359</v>
+        <v>-15.99323676837237</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-13.35417831056174</v>
+        <v>-13.31001371805941</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-16.46323963834088</v>
+        <v>-16.40886916099574</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-21.30440005838761</v>
+        <v>-21.23387087966424</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-16.25871465814627</v>
+        <v>-16.20473731938319</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-27.00587247576843</v>
+        <v>-26.91584416945391</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-21.93508783791174</v>
+        <v>-21.86212958811627</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-27.93249337936749</v>
+        <v>-27.84008849433977</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-28.14480703816263</v>
+        <v>-28.05181420681487</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-33.26057659651632</v>
+        <v>-33.15009960098266</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-33.69075156718377</v>
+        <v>-33.57873393157605</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-25.7308543820609</v>
+        <v>-25.645321648195</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>42</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.649418822646631</v>
+        <v>4.633339240006379</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.869224417973278</v>
+        <v>-8.839224020356227</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.644347339424904</v>
+        <v>2.635436903220338</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-6.755826587588132</v>
+        <v>-6.733090889873921</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-14.44683826866152</v>
+        <v>-14.39815319515871</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-21.30497360450772</v>
+        <v>-21.23295320587211</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-9.472068738345747</v>
+        <v>-9.439951209937327</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-9.942792058100437</v>
+        <v>-9.908688609089737</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.234540124957007</v>
+        <v>-5.216638575379683</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.087720339518398</v>
+        <v>-6.067395030568477</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.294484498590414</v>
+        <v>-6.273577635355259</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.874253854829213</v>
+        <v>-3.861032740162386</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-13.85065020618265</v>
+        <v>-13.80350428309085</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-13.60364993063835</v>
+        <v>-13.55740956028175</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-18.20772403449504</v>
+        <v>-18.14595443816245</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-25.54032381130389</v>
+        <v>-25.45269796703128</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-23.08344798713277</v>
+        <v>-23.00454594355673</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-20.09979815047849</v>
+        <v>-20.03096345801578</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-17.78398692858685</v>
+        <v>-17.72290204365598</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-26.07371251699693</v>
+        <v>-25.98392332684298</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-26.16538663229951</v>
+        <v>-26.07552477810534</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-35.22782473639711</v>
+        <v>-35.10655175558185</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-26.70853122910928</v>
+        <v>-26.61682270671509</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-24.70351240052002</v>
+        <v>-24.61910649552043</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-19.18586891684147</v>
+        <v>-19.12044802416511</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-13.42593232619515</v>
+        <v>-13.37977518259798</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.71772621228871</v>
+        <v>-16.6598193778164</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-16.47153813246392</v>
+        <v>-16.4145524174246</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>37</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6.966021139249484</v>
+        <v>6.942027909780364</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.355786459803014</v>
+        <v>5.338380324069988</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.150308795886168</v>
+        <v>-3.138741997352618</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.020852604037593</v>
+        <v>-3.009687995059906</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.266315130009318</v>
+        <v>-6.243841196636879</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.970448377391598</v>
+        <v>-5.948373749439497</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.056906006404482</v>
+        <v>-6.034775341008064</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.819311341051865</v>
+        <v>-3.804196441936753</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6.589630010346362</v>
+        <v>-6.565653342957674</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.443282481306817</v>
+        <v>-7.416874919503904</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.94049094939561</v>
+        <v>-4.923018943357022</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-7.618200974204363</v>
+        <v>-7.591219492998675</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-21.59917608666704</v>
+        <v>-21.52330215855885</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-24.0664267743739</v>
+        <v>-23.98211998499217</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>49</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>10.77186780223901</v>
+        <v>10.73400124185238</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.03859139844127</v>
+        <v>3.028890944572446</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.811937794485</v>
+        <v>10.77491389019089</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.817739824290797</v>
+        <v>4.801733088665401</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.365937044692458</v>
+        <v>8.337728200136496</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10.70927803971401</v>
+        <v>10.67349586405372</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8.583159805942252</v>
+        <v>8.554572404490983</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>14.25095295174979</v>
+        <v>14.20318398693822</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.10344963605646</v>
+        <v>10.06956680357913</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.254219651080504</v>
+        <v>9.222808511025988</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.005308277117599</v>
+        <v>6.981382491117103</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.9007032197348437</v>
+        <v>0.8984988739858508</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.5256677397308</v>
+        <v>2.51887738468406</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.824778714945118</v>
+        <v>4.809937378493764</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>56</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7077240344956834</v>
+        <v>-0.705891577380271</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.892399445549486</v>
+        <v>-5.870647498949552</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-6.289082860093572</v>
+        <v>-6.266411285141807</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.586183807421072</v>
+        <v>-2.576344601541017</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.600042724754374</v>
+        <v>7.573745522036702</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.899711265927124</v>
+        <v>7.872884334764464</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7.816975926230619</v>
+        <v>7.790290332182117</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.92900936146142</v>
+        <v>10.89167207890645</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10.87103234060094</v>
+        <v>10.83345006221719</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.65168615409749</v>
+        <v>4.635725892903054</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.657218450433504</v>
+        <v>2.648054337081049</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.263638457368728</v>
+        <v>-6.240451989917531</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.269906778599385</v>
+        <v>2.263830253892728</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7290202022680035</v>
+        <v>0.7283047254333468</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>51</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-7.395399104523698</v>
+        <v>-7.36941591325651</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.681063828409613</v>
+        <v>6.658157359190831</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4021979063127858</v>
+        <v>0.4014324548112143</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.419836671361601</v>
+        <v>6.397518041545332</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.919731931878999</v>
+        <v>3.905915394242207</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.291434424740288</v>
+        <v>0.291225319880283</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.64955568067743</v>
+        <v>-7.62130514603308</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.2615734138827221</v>
+        <v>-0.259697146869776</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3225690836845843</v>
+        <v>-0.3209342016662475</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-11.0032833040588</v>
+        <v>-10.96331040144744</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-11.21154362490498</v>
+        <v>-11.1710089170686</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.347270583386553</v>
+        <v>-1.341110676452061</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.70462899410694</v>
+        <v>-5.682152642733307</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.487833013177934</v>
+        <v>-3.473375946837251</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>71</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.027688440353401</v>
+        <v>1.023609378652942</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.219512497925969</v>
+        <v>-6.19579388854779</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.9794132888979519</v>
+        <v>-0.9751271259088412</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5603081487719876</v>
+        <v>0.5587559871363723</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.02151812353265115</v>
+        <v>0.02155263534925211</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.091351569077212</v>
+        <v>-1.086485551763936</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.998409964314504</v>
+        <v>-3.982604532606416</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.878911550100241</v>
+        <v>-5.856324426330779</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.941498838982994</v>
+        <v>-5.919155576296362</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.676465816097526</v>
+        <v>1.67121393939177</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.884123282717418</v>
+        <v>2.874248480957469</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.918785777771561</v>
+        <v>2.909478558878916</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.910264002931918</v>
+        <v>3.898176742744887</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.74834206540622</v>
+        <v>2.740377160040183</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>84</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.255343082114734</v>
+        <v>-7.228420940447791</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.724664237451158</v>
+        <v>-1.71680332947281</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2620541785399126</v>
+        <v>0.261858811898648</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7990056509803694</v>
+        <v>-0.7955098849171236</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.429221042679096</v>
+        <v>3.416427640040354</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.112154166918103</v>
+        <v>6.090118550323631</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.06600439766582866</v>
+        <v>0.06721743296800753</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.788013826312429</v>
+        <v>-2.776049542457621</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.309669005150049</v>
+        <v>4.294421194493069</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.071430314286225</v>
+        <v>1.068220551867775</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.642284306930463</v>
+        <v>5.621582199179493</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>10.45488364138832</v>
+        <v>10.41678641636936</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.646081708217743</v>
+        <v>7.6193871049961</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15.06872574918646</v>
+        <v>15.01401901114683</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>64</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.493438320210331</v>
+        <v>-2.483606849814493</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9804234205858435</v>
+        <v>-0.9750740842324106</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.502661141727501</v>
+        <v>-4.484587879008203</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.80974939652814</v>
+        <v>-2.798387875944421</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.478133927717877</v>
+        <v>-6.453482009901279</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-9.312017656551362</v>
+        <v>-9.275849389271727</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-10.96545528242222</v>
+        <v>-10.92187325772377</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-9.87137827942832</v>
+        <v>-9.831720147269472</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.934856062141428</v>
+        <v>-9.896128614640453</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.090348969722314</v>
+        <v>-6.066226750477654</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-7.864135858767</v>
+        <v>-7.833932227301602</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-9.399819552376456</v>
+        <v>-9.363419063552072</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-9.825420755743842</v>
+        <v>-9.786261499197458</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-8.008479367579014</v>
+        <v>-7.977052417424247</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>98</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7.710643312443551</v>
+        <v>7.680650910757748</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6.100789646921839</v>
+        <v>6.078430330163847</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>7.749545833753395</v>
+        <v>7.720110490540549</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.796909324995532</v>
+        <v>3.78273271217094</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.302392798712042</v>
+        <v>5.281723161755835</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.557615654825632</v>
+        <v>3.544727108446779</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.517687505583538</v>
+        <v>5.49830369368464</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.028308833355403</v>
+        <v>4.015013056350135</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.946047926234783</v>
+        <v>2.935800015074285</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.04806486092110163</v>
+        <v>0.04912673975764648</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.8666067562860462</v>
+        <v>0.8638092738964858</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.948611764924777</v>
+        <v>2.938025706215086</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.550654827691126</v>
+        <v>3.538903970890829</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.319061228285115</v>
+        <v>-1.312511601098301</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.052016225244422</v>
+        <v>2.057817629823852</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.090054073333278</v>
+        <v>1.092251369309878</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.294379049641798</v>
+        <v>3.303022498978486</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.675620856098192</v>
+        <v>6.693277416061768</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7.439209065377639</v>
+        <v>7.45941908986569</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.787913778859043</v>
+        <v>5.802927130476711</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8.306671901960677</v>
+        <v>8.327733174485395</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>8.491533494207431</v>
+        <v>8.512828783283446</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.433647375418637</v>
+        <v>8.455559876048071</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>8.234758597586961</v>
+        <v>8.256001620559445</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.63818881141771</v>
+        <v>10.66639029851225</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10.67587064602188</v>
+        <v>10.70403479946266</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>8.952523959451788</v>
+        <v>8.975258468594483</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10.87753895916703</v>
+        <v>10.9057090204839</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.1250172675784</v>
+        <v>-5.280144304133003</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.790234840595943</v>
+        <v>-2.885694803247389</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.485113713041819</v>
+        <v>-3.592613371057062</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.040925097639459</v>
+        <v>-2.098396187622264</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.219064568178908</v>
+        <v>-2.274775088632374</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.878263227876296</v>
+        <v>-2.966759223193783</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.325191317422437</v>
+        <v>-0.3379747652050824</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7821828109068036</v>
+        <v>-0.8123539577663834</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1888103252495981</v>
+        <v>-0.1907928931841454</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.318842781677134</v>
+        <v>-4.453266446282278</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.526942762916192</v>
+        <v>-4.657997178505838</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.123500857552123</v>
+        <v>-4.243462038116469</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.149963332960475</v>
+        <v>-4.283321368748354</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.573401592073878</v>
+        <v>-4.713872145315754</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.97260498687664</v>
+        <v>-2.013135364901942</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.51212669506512</v>
+        <v>4.595398375745347</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9927816144740191</v>
+        <v>1.010973739958743</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3620464228845179</v>
+        <v>0.3719541491437823</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.819065316268322</v>
+        <v>-3.888754120563718</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.167273425559593</v>
+        <v>1.189498865546192</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1933284293574644</v>
+        <v>-0.1992496818230123</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.995512492343167</v>
+        <v>3.051489512179728</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8464516285888948</v>
+        <v>0.8660118286553811</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.013079430797724</v>
+        <v>0.0102503804191727</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6205995086506633</v>
+        <v>0.6364913209197383</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.430590810706526</v>
+        <v>-1.456785096202921</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.815513657834721</v>
+        <v>1.846364548171451</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.071760082475983</v>
+        <v>-1.095403481254387</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.656229017884399</v>
+        <v>-3.724220262385749</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.011988677360144</v>
+        <v>-7.138271328492571</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.662671337445246</v>
+        <v>-5.763712239056403</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.113813553674824</v>
+        <v>-6.219454949818939</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-7.233630117584461</v>
+        <v>-7.359761266487105</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.354792831031453</v>
+        <v>-6.467425500794924</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.439526548303732</v>
+        <v>-6.555972640041375</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.841631983468218</v>
+        <v>-4.928126382728834</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6.909174507927574</v>
+        <v>-7.02845892272753</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.674174103066633</v>
+        <v>-5.777790983618161</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.463448557666645</v>
+        <v>-6.574260284266963</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.007960124002139</v>
+        <v>-7.131593103253032</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-10.32393866592992</v>
+        <v>-10.51042759585487</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-10.65998877651435</v>
+        <v>-10.85242223990981</v>
       </c>
     </row>
     <row r="24">
@@ -2185,10 +2185,8 @@
           <t>X &gt; -0.5011</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4006~4019</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4006</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.007183725074916936</v>
@@ -2239,10 +2237,8 @@
           <t>X &gt; -0.4838</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3984~3997</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3984</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.07912758716018686</v>
@@ -2293,10 +2289,8 @@
           <t>X &gt; -0.4665</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3947~3960</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3947</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.09444842122007202</v>
@@ -2347,10 +2341,8 @@
           <t>X &gt; -0.4493</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3904~3917</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3904</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.1829966556707916</v>
@@ -2401,10 +2393,8 @@
           <t>X &gt; -0.432</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3865~3878</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3865</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.09529494733735788</v>
@@ -2455,10 +2445,8 @@
           <t>X &gt; -0.4147</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3823~3836</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3823</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.1472443681766009</v>
@@ -2509,10 +2497,8 @@
           <t>X &gt; -0.3974</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3788~3801</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3788</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.01905839118176544</v>
@@ -2563,10 +2549,8 @@
           <t>X &gt; -0.3802</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3751~3764</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3751</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.04923003115577984</v>
@@ -2617,10 +2601,8 @@
           <t>X &gt; -0.3629</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3702~3715</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3702</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.1919578356877665</v>
@@ -2671,10 +2653,8 @@
           <t>X &gt; -0.3456</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3646~3659</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3646</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.1840641742684639</v>
@@ -2725,10 +2705,8 @@
           <t>X &gt; -0.3283</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3595~3608</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3595</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.08213011621884192</v>
@@ -2779,10 +2757,8 @@
           <t>X &gt; -0.311</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3524~3537</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3524</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.1044080685843056</v>
@@ -2833,10 +2809,8 @@
           <t>X &gt; -0.2938</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3440~3453</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3440</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.06955038526352553</v>
@@ -2887,10 +2861,8 @@
           <t>X &gt; -0.2765</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3376~3389</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3376</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.1179514702887019</v>
@@ -2941,10 +2913,8 @@
           <t>X &gt; -0.2592</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3278~3291</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3278</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.1081450962658934</v>
@@ -2995,10 +2965,8 @@
           <t>X &gt; -0.2419</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3125~3137</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3125</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.2141906313352564</v>
@@ -3049,10 +3017,8 @@
           <t>X &gt; -0.2246</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2978~2985</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2978</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.03587491262084797</v>
@@ -3103,10 +3069,8 @@
           <t>X &gt; -0.2074</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2790~2793</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2790</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.1739444223607336</v>
@@ -3157,10 +3121,8 @@
           <t>X &gt; -0.1901</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2621~2621</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2621</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.4252949876877707</v>
@@ -3211,10 +3173,8 @@
           <t>X &gt; -0.1728</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2493~2493</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2493</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.016389196837764</v>
@@ -3265,10 +3225,8 @@
           <t>X &gt; -0.1555</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2333~2333</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2333</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.8713280749893357</v>
@@ -3319,10 +3277,8 @@
           <t>X &gt; -0.1382</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2175~2175</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2175</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.161734093583128</v>
@@ -3373,10 +3329,8 @@
           <t>X &gt; -0.121</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2010~2010</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2010</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.586163669839777</v>
@@ -3427,10 +3381,8 @@
           <t>X &gt; -0.1037</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1815~1815</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1815</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.225569944252832</v>
@@ -3481,10 +3433,8 @@
           <t>X &gt; -0.0864</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1593~1593</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1593</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.994948371566551</v>
@@ -3535,10 +3485,8 @@
           <t>X &gt; -0.06912</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1379~1379</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1379</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.618961969855292</v>
@@ -3589,10 +3537,8 @@
           <t>X &gt; -0.05184</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1145~1145</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1145</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.576430675423211</v>
@@ -3643,10 +3589,8 @@
           <t>X &gt; -0.03456</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>898~898</t>
-        </is>
+      <c r="B33" t="n">
+        <v>898</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.85400043257399</v>
@@ -3697,10 +3641,8 @@
           <t>X &gt; -0.01728</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>661~661</t>
-        </is>
+      <c r="B34" t="n">
+        <v>661</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.423354418065372</v>
@@ -3751,10 +3693,8 @@
           <t>X &gt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0~0</t>
-        </is>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -3911,10 +3851,8 @@
           <t>X &lt; -0.5011</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.723429149669542</v>
@@ -3965,10 +3903,8 @@
           <t>X &lt; -0.4838</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>105~105</t>
-        </is>
+      <c r="B7" t="n">
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>4.649418822647164</v>
@@ -4019,10 +3955,8 @@
           <t>X &lt; -0.4665</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>142~142</t>
-        </is>
+      <c r="B8" t="n">
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3.844589848804112</v>
@@ -4073,10 +4007,8 @@
           <t>X &lt; -0.4493</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>185~185</t>
-        </is>
+      <c r="B9" t="n">
+        <v>185</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4.803858977087323</v>
@@ -4127,10 +4059,8 @@
           <t>X &lt; -0.432</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>224~224</t>
-        </is>
+      <c r="B10" t="n">
+        <v>224</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2.417275965504317</v>
@@ -4181,10 +4111,8 @@
           <t>X &lt; -0.4147</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>266~266</t>
-        </is>
+      <c r="B11" t="n">
+        <v>266</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>2.769719574526874</v>
@@ -4235,10 +4163,8 @@
           <t>X &lt; -0.3974</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>301~301</t>
-        </is>
+      <c r="B12" t="n">
+        <v>301</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.3304819455707602</v>
@@ -4289,10 +4215,8 @@
           <t>X &lt; -0.3802</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>338~338</t>
-        </is>
+      <c r="B13" t="n">
+        <v>338</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.056857537778185</v>
@@ -4343,10 +4267,8 @@
           <t>X &lt; -0.3629</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>387~387</t>
-        </is>
+      <c r="B14" t="n">
+        <v>387</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2.286923436895968</v>
@@ -4397,10 +4319,8 @@
           <t>X &lt; -0.3456</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>443~443</t>
-        </is>
+      <c r="B15" t="n">
+        <v>443</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.908367548864518</v>
@@ -4451,10 +4371,8 @@
           <t>X &lt; -0.3283</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>494~494</t>
-        </is>
+      <c r="B16" t="n">
+        <v>494</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.9478572263487308</v>
@@ -4505,10 +4423,8 @@
           <t>X &lt; -0.311</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>565~565</t>
-        </is>
+      <c r="B17" t="n">
+        <v>565</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.9578891134183394</v>
@@ -4559,10 +4475,8 @@
           <t>X &lt; -0.2938</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>649~649</t>
-        </is>
+      <c r="B18" t="n">
+        <v>649</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.1051486437847018</v>
@@ -4613,10 +4527,8 @@
           <t>X &lt; -0.2765</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>713~713</t>
-        </is>
+      <c r="B19" t="n">
+        <v>713</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3195252767317172</v>
@@ -4667,10 +4579,8 @@
           <t>X &lt; -0.2592</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>811~811</t>
-        </is>
+      <c r="B20" t="n">
+        <v>811</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.6508280176445211</v>
@@ -4721,10 +4631,8 @@
           <t>X &lt; -0.2419</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>964~965</t>
-        </is>
+      <c r="B21" t="n">
+        <v>964</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.8744373274584163</v>
@@ -4775,10 +4683,8 @@
           <t>X &lt; -0.2246</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1111~1117</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1111</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.0580388507837597</v>
@@ -4829,10 +4735,8 @@
           <t>X &lt; -0.2074</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1299~1309</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1299</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.239809595993016</v>
@@ -4883,10 +4787,8 @@
           <t>X &lt; -0.1901</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1468~1481</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1468</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.6365848428298264</v>
@@ -4937,10 +4839,8 @@
           <t>X &lt; -0.1728</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1596~1609</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1596</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.467956654579154</v>
@@ -4991,10 +4891,8 @@
           <t>X &lt; -0.1555</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1756~1769</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1756</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.051945951640157</v>
@@ -5045,10 +4943,8 @@
           <t>X &lt; -0.1382</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1914~1927</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1914</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.222031989125384</v>
@@ -5099,10 +4995,8 @@
           <t>X &lt; -0.121</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2079~2092</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2079</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.441813081204238</v>
@@ -5153,10 +5047,8 @@
           <t>X &lt; -0.1037</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2274~2287</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2274</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.8974610574202941</v>
@@ -5207,10 +5099,8 @@
           <t>X &lt; -0.0864</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2496~2509</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2496</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.198101532645204</v>
@@ -5261,10 +5151,8 @@
           <t>X &lt; -0.06912</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2710~2723</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2710</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.263177578381104</v>
@@ -5315,10 +5203,8 @@
           <t>X &lt; -0.05184</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2944~2957</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2944</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.326715290111906</v>
@@ -5369,10 +5255,8 @@
           <t>X &lt; -0.03456</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3191~3204</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3191</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-1.026521965653174</v>
@@ -5423,10 +5307,8 @@
           <t>X &lt; -0.01728</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3428~3441</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3428</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.4155539842611233</v>
@@ -5477,10 +5359,8 @@
           <t>X &lt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3732~3745</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3732</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1836919917720508</v>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_90.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_90.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-90 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-90 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.63737772255789</v>
+        <v>15.64987030338444</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.092754778058932</v>
+        <v>-4.079888434842836</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.487713950206306</v>
+        <v>-4.474747146054561</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.709492803147171</v>
+        <v>4.722441008868387</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.173344962042336</v>
+        <v>4.186427361678192</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.007665680144775</v>
+        <v>9.020685857048584</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.387818611969521</v>
+        <v>4.40086292416462</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.46094267849994</v>
+        <v>8.47410629237163</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.402294315311742</v>
+        <v>8.415478448523658</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>16.63683114232944</v>
+        <v>16.65022648334595</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>20.97850534813506</v>
+        <v>20.99195605671297</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.47500479394618</v>
+        <v>16.48845210856744</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.51466962955441</v>
+        <v>11.52822284642252</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.76726576439357</v>
+        <v>11.75683612869749</v>
       </c>
     </row>
     <row r="7">
@@ -627,98 +627,98 @@
         <v>37</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.555232738093281</v>
+        <v>1.567713359318304</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.05080617399298148</v>
+        <v>-0.03793742144619472</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.139936886417068</v>
+        <v>-3.126969780426997</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.46868105226071</v>
+        <v>10.48163252788074</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.237468941628286</v>
+        <v>7.250552719382462</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.838940480303265</v>
+        <v>4.851958250882248</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6402350246329931</v>
+        <v>-0.627193265149856</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.80561548373803</v>
+        <v>-3.79245679663461</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.867332626860623</v>
+        <v>-3.854152603715207</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.082165952587374</v>
+        <v>6.095558504439424</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.28048035715968</v>
+        <v>11.29392916160701</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.616455664596302</v>
+        <v>8.629901928025852</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.198513511175499</v>
+        <v>8.212066483894674</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.747609744737559</v>
+        <v>5.737180109039407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.4579</t>
+          <t>X ≈ -0.4578</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.944907562399401</v>
+        <v>7.957392791567706</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.97752339642548</v>
+        <v>10.99039996384856</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.5864910075444</v>
+        <v>10.59946712726971</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.079630724367597</v>
+        <v>6.092578902004739</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.18445101354891</v>
+        <v>10.19753606179427</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15.12564045933271</v>
+        <v>15.13866315512368</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.40221206695468</v>
+        <v>10.41525838122787</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.97226509826023</v>
+        <v>2.985425963112903</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>14.5253009193816</v>
+        <v>14.53848655882071</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.35633033224683</v>
+        <v>11.36972404241409</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>13.47848763802199</v>
+        <v>13.49193674642584</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.84082308736939</v>
+        <v>15.85427019772489</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>17.74976419424463</v>
+        <v>17.76331774126459</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>15.67847083839041</v>
+        <v>15.66804120269014</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>39</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-8.874460827689731</v>
+        <v>-8.861990819777169</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-10.48309734563932</v>
+        <v>-10.47023847821293</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-15.99323676837237</v>
+        <v>-15.9802806527187</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-13.31001371805941</v>
+        <v>-13.2970790517522</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-16.40886916099574</v>
+        <v>-16.39580050821849</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-21.23387087966424</v>
+        <v>-21.22086786730577</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-16.20473731938319</v>
+        <v>-16.19170376687072</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-26.91584416945391</v>
+        <v>-26.90269568819237</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-21.86212958811627</v>
+        <v>-21.84895628455558</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-27.84008849433977</v>
+        <v>-27.82670544300109</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-28.05181420681487</v>
+        <v>-28.0383735458155</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-33.15009960098266</v>
+        <v>-33.13665910957951</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-33.57873393157605</v>
+        <v>-33.56518384677565</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-25.645321648195</v>
+        <v>-25.65575128389198</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>42</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.633339240006379</v>
+        <v>4.645819953851081</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.839224020356227</v>
+        <v>-8.8263650611649</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.635436903220338</v>
+        <v>2.648405668868577</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-6.733090889873921</v>
+        <v>-6.720152863838301</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-14.39815319515871</v>
+        <v>-14.38508440625466</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-21.23295320587211</v>
+        <v>-21.21995127604938</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-9.439951209937327</v>
+        <v>-9.426915276370138</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-9.908688609089737</v>
+        <v>-9.895534076468309</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.216638575379683</v>
+        <v>-5.203460279554186</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.067395030568477</v>
+        <v>-6.054006652648646</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.273577635355259</v>
+        <v>-6.260132979588221</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.861032740162386</v>
+        <v>-3.847588587793794</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-13.80350428309085</v>
+        <v>-13.78995301992238</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-13.55740956028175</v>
+        <v>-13.56783919597882</v>
       </c>
     </row>
     <row r="11">
@@ -835,98 +835,98 @@
         <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-18.14595443816245</v>
+        <v>-18.13349504218277</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-25.45269796703128</v>
+        <v>-25.43985403236307</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-23.00454594355673</v>
+        <v>-22.99159750870542</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-20.03096345801578</v>
+        <v>-20.0180355995835</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-17.72290204365598</v>
+        <v>-17.70983636683081</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-25.98392332684298</v>
+        <v>-25.97092510759968</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-26.07552477810534</v>
+        <v>-26.06249765059695</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-35.10655175558185</v>
+        <v>-35.09340836150891</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-26.61682270671509</v>
+        <v>-26.60365230793876</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-24.61910649552043</v>
+        <v>-24.60572365591878</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-19.12044802416511</v>
+        <v>-19.10700633400586</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-13.37977518259798</v>
+        <v>-13.36633253209725</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.6598193778164</v>
+        <v>-16.64626843023763</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-16.4145524174246</v>
+        <v>-16.42498205312405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.3888</t>
+          <t>X ≈ -0.3887</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>37</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6.942027909780364</v>
+        <v>6.95450888198247</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.338380324069988</v>
+        <v>5.35124875651028</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.138741997352618</v>
+        <v>-3.125779544478782</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.009687995059906</v>
+        <v>-2.996749326113431</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.243841196636879</v>
+        <v>-6.23076927640021</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.948373749439497</v>
+        <v>-5.935365303130475</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.034775341008064</v>
+        <v>-6.021739260714646</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.804196441936753</v>
+        <v>-3.791040730746694</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6.565653342957674</v>
+        <v>-6.552476553386704</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.416874919503904</v>
+        <v>-7.403487755912657</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.923018943357022</v>
+        <v>-4.9095746056176</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-7.591219492998675</v>
+        <v>-7.577776241498484</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-21.52330215855885</v>
+        <v>-21.50975167705382</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-23.98211998499217</v>
+        <v>-23.99254962069032</v>
       </c>
     </row>
     <row r="13">
@@ -939,98 +939,98 @@
         <v>49</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>10.73400124185238</v>
+        <v>10.74648499124407</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.028890944572446</v>
+        <v>3.041756504504171</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.77491389019089</v>
+        <v>10.78788637883697</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.801733088665401</v>
+        <v>4.814676449322384</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.337728200136496</v>
+        <v>8.350808672109089</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10.67349586405372</v>
+        <v>10.68651310623521</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8.554572404490983</v>
+        <v>8.56761514644441</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>14.20318398693822</v>
+        <v>14.21634693665609</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.06956680357913</v>
+        <v>10.0827490855994</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.222808511025988</v>
+        <v>9.236200056991194</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.981382491117103</v>
+        <v>6.994829106009199</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.8984988739858508</v>
+        <v>0.9119431276246743</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.51887738468406</v>
+        <v>2.532429453716951</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.809937378493764</v>
+        <v>4.799507742795612</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.3543</t>
+          <t>X ≈ -0.3542</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>56</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.705891577380271</v>
+        <v>-0.6934197803810562</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.870647498949552</v>
+        <v>-5.857791143500265</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-6.266411285141807</v>
+        <v>-6.253453599407358</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.576344601541017</v>
+        <v>-2.563407704810082</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.573745522036702</v>
+        <v>7.586824760872169</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.872884334764464</v>
+        <v>7.885899332185019</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7.790290332182117</v>
+        <v>7.803332118238217</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.89167207890645</v>
+        <v>10.9048331915369</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10.83345006221719</v>
+        <v>10.84663226069081</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.635725892903054</v>
+        <v>4.649115746129141</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.648054337081049</v>
+        <v>2.661499711475031</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.240451989917531</v>
+        <v>-6.227009037993689</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.263830253892728</v>
+        <v>2.277382193395837</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7283047254333468</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>51</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-7.36941591325651</v>
+        <v>-7.35695230507428</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.658157359190831</v>
+        <v>6.67102355487355</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4014324548112143</v>
+        <v>0.4143941717740631</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.397518041545332</v>
+        <v>6.41046054463007</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.905915394242207</v>
+        <v>3.918991299383912</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.291225319880283</v>
+        <v>0.3042349439993473</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.62130514603308</v>
+        <v>-7.60827229672222</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.259697146869776</v>
+        <v>-0.2465416498714958</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3209342016662475</v>
+        <v>-0.3077566833789049</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.96331040144744</v>
+        <v>-10.94992578282389</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-11.1710089170686</v>
+        <v>-11.1575670837478</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.341110676452061</v>
+        <v>-1.327667274158593</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.682152642733307</v>
+        <v>-5.668601436008984</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.473375946837251</v>
+        <v>-3.483805582533627</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>71</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.023609378652942</v>
+        <v>1.036079460295802</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.19579388854779</v>
+        <v>-6.182941365307791</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.9751271259088412</v>
+        <v>-0.9621681846828807</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5587559871363723</v>
+        <v>0.571692706853888</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.02155263534925211</v>
+        <v>0.03462462229657604</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.086485551763936</v>
+        <v>-1.073477960579496</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.982604532606416</v>
+        <v>-3.969570939862543</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.856324426330779</v>
+        <v>-5.843172517936082</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.919155576296362</v>
+        <v>-5.905981047721959</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.67121393939177</v>
+        <v>1.684601792137144</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.874248480957469</v>
+        <v>2.887693076974536</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.909478558878916</v>
+        <v>2.922922328457915</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.898176742744887</v>
+        <v>3.91172853605427</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.740377160040183</v>
+        <v>2.729947524341391</v>
       </c>
     </row>
     <row r="17">
@@ -1147,98 +1147,98 @@
         <v>84</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.228420940447791</v>
+        <v>-7.21596217711587</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.71680332947281</v>
+        <v>-1.703949138553234</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.261858811898648</v>
+        <v>0.2748166878249521</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7955098849171236</v>
+        <v>-0.7825761957812816</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.416427640040354</v>
+        <v>3.429500457179515</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.090118550323631</v>
+        <v>6.103129354774794</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.06721743296800753</v>
+        <v>0.0802518362968172</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.776049542457621</v>
+        <v>-2.762897520279225</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.294421194493069</v>
+        <v>4.307598829711154</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.068220551867775</v>
+        <v>1.081607444974438</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.621582199179493</v>
+        <v>5.635026949223239</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>10.41678641636936</v>
+        <v>10.43023108887122</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.6193871049961</v>
+        <v>7.63293903323364</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15.01401901114683</v>
+        <v>15.00358937544839</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.2852</t>
+          <t>X ≈ -0.2851</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.483606849814493</v>
+        <v>-2.471145818408438</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9750740842324106</v>
+        <v>-0.9622216381303303</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.484587879008203</v>
+        <v>-4.47163671733464</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.798387875944421</v>
+        <v>-2.78545795937044</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.453482009901279</v>
+        <v>-6.440418509298262</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-9.275849389271727</v>
+        <v>-9.26285056927091</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-10.92187325772377</v>
+        <v>-10.90884698915002</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-9.831720147269472</v>
+        <v>-9.818573171461374</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.896128614640453</v>
+        <v>-9.88295804123878</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.066226750477654</v>
+        <v>-6.05284314295308</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-7.833932227301602</v>
+        <v>-7.820491502092267</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-9.363419063552072</v>
+        <v>-9.34997811652719</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-9.786261499197458</v>
+        <v>-9.772711250996437</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-7.977052417424247</v>
+        <v>-7.987482053122399</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7.680650910757748</v>
+        <v>8.093502984765408</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6.078430330163847</v>
+        <v>6.491794223813478</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>7.720110490540549</v>
+        <v>8.113152728037207</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.78273271217094</v>
+        <v>4.216970866823246</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.281723161755835</v>
+        <v>5.695667840036243</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.544727108446779</v>
+        <v>3.979294961902411</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.49830369368464</v>
+        <v>5.912457519153136</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.015013056350135</v>
+        <v>4.439696779783041</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.935800015074285</v>
+        <v>3.3709233984546</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.04912673975764648</v>
+        <v>0.5051789583613626</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.8638092738964858</v>
+        <v>1.309755908417472</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.938025706215086</v>
+        <v>2.354017434694434</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.538903970890829</v>
+        <v>2.944518272422492</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.312511601098301</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>153</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.057817629823852</v>
+        <v>1.759605826077646</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.092251369309878</v>
+        <v>0.8077338680152764</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.303022498978486</v>
+        <v>3.019045525926977</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.693277416061768</v>
+        <v>6.407429557117354</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7.45941908986569</v>
+        <v>7.175602012576014</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.802927130476711</v>
+        <v>5.519486700751266</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8.327733174485395</v>
+        <v>8.045802701489137</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>8.512828783283446</v>
+        <v>8.234585784647429</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.455559876048071</v>
+        <v>8.175698221678545</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>8.256001620559445</v>
+        <v>7.982220510555663</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.66639029851225</v>
+        <v>10.39186096900677</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10.70403479946266</v>
+        <v>11.08273115032303</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>8.975258468594483</v>
+        <v>9.359519418788679</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10.9057090204839</v>
+        <v>10.89527938478574</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>147</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.280144304133003</v>
+        <v>-5.62178981713884</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.885694803247389</v>
+        <v>-2.871193475739751</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.592613371057062</v>
+        <v>-3.948497286276933</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.098396187622264</v>
+        <v>-2.084353768496847</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.274775088632374</v>
+        <v>-2.631026380878474</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.966759223193783</v>
+        <v>-3.323747578792478</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3379747652050824</v>
+        <v>-0.3245603327612372</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.8123539577663834</v>
+        <v>-0.7986261095900176</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1907928931841454</v>
+        <v>-0.1773508945071143</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.453266446282278</v>
+        <v>-4.438156850177144</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.657997178505838</v>
+        <v>-4.642866160783889</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.243462038116469</v>
+        <v>-4.610161732440297</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.283321368748354</v>
+        <v>-4.655601038641102</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.713872145315754</v>
+        <v>-4.724301781013907</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>188</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.013135364901942</v>
+        <v>-2.000613075226319</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.595398375745347</v>
+        <v>4.319144180367111</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.010973739958743</v>
+        <v>1.023980871376345</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3719541491437823</v>
+        <v>0.09699906696587846</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.888754120563718</v>
+        <v>-3.875643316188778</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.189498865546192</v>
+        <v>1.202541761840557</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1992496818230123</v>
+        <v>-0.4771599866105518</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.051489512179728</v>
+        <v>3.063736040907848</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8660118286553811</v>
+        <v>0.8789413976166998</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0102503804191727</v>
+        <v>0.0238003181369919</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6364913209197383</v>
+        <v>0.3515834628226884</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.456785096202921</v>
+        <v>-1.443332807482811</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.846364548171451</v>
+        <v>1.859920594523054</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.095403481254387</v>
+        <v>-1.105833116952539</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>169</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.724220262385749</v>
+        <v>-3.711697972710127</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.138271328492571</v>
+        <v>-7.12536151891652</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.763712239056403</v>
+        <v>-5.750705107638801</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.219454949818939</v>
+        <v>-6.206475807420475</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-7.359761266487105</v>
+        <v>-7.346650462112166</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.467425500794924</v>
+        <v>-6.454382604500559</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.555972640041375</v>
+        <v>-6.542906385740899</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.928126382728834</v>
+        <v>-5.241182803823882</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7.02845892272753</v>
+        <v>-7.340672108719055</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.777790983618161</v>
+        <v>-6.097027334598046</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.574260284266963</v>
+        <v>-6.560802990556745</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.131593103253032</v>
+        <v>-7.118140814532921</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-10.51042759585487</v>
+        <v>-10.49687154950327</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-10.85242223990981</v>
+        <v>-10.86285187560796</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-11.08718832020998</v>
+        <v>-11.39564471270489</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-11.13626193317423</v>
+        <v>-11.4564432088695</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-13.09363063977082</v>
+        <v>-13.40160219052376</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-10.61962750716332</v>
+        <v>-10.94579565158639</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.689298722235492</v>
+        <v>-6.057728615534977</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.173106784519831</v>
+        <v>-6.535548384349497</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.82034050179211</v>
+        <v>-8.170646340514715</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-8.287523900573611</v>
+        <v>-8.637714984301631</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-8.348523786755912</v>
+        <v>-8.698697140824407</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-8.41739897178384</v>
+        <v>-8.773422138704831</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-9.403402296101596</v>
+        <v>-9.753317095414637</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-7.025269138755988</v>
+        <v>-7.393357547710302</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-5.883023749700889</v>
+        <v>-6.263120804124483</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-4.852052417424602</v>
+        <v>-4.486997556998723</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.131561679790174</v>
+        <v>3.493926736761388</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.519988066825917</v>
+        <v>1.882740643697559</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.125119360229178</v>
+        <v>1.487969258942378</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.13037249283682</v>
+        <v>3.504986855360926</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.966951277764359</v>
+        <v>2.337766484655027</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2356067845198382</v>
+        <v>0.1194172438500019</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.57034050179211</v>
+        <v>-1.223154750636432</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.287523900573603</v>
+        <v>-2.948085029643153</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-4.895859638996114</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.69864897178384</v>
+        <v>-6.374709252935894</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-8.153402296101561</v>
+        <v>-7.837272046416501</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-11.86901913875599</v>
+        <v>-11.57647879972141</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-12.91427374970089</v>
+        <v>-12.62556047064488</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-13.2895524174246</v>
+        <v>-13.65768645563848</v>
       </c>
     </row>
     <row r="26">
@@ -1615,358 +1615,358 @@
         <v>158</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.12634971261518</v>
+        <v>-3.113827422939558</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.122836168091588</v>
+        <v>4.135745977667639</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.158347208330447</v>
+        <v>8.171354339748049</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.022777556127679</v>
+        <v>7.035756698526143</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>8.383090518270983</v>
+        <v>8.396201322645922</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.148886886366391</v>
+        <v>6.161929782660756</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.000862029853458</v>
+        <v>1.013928284153934</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.630878330953358</v>
+        <v>-2.61769732165812</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.957701001945644</v>
+        <v>-3.944502262990881</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.542003402163587</v>
+        <v>-3.528598274510756</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.01257951129115</v>
+        <v>-4.999122217580933</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.765539572485842</v>
+        <v>-4.751983526134239</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.781641025019681</v>
+        <v>-5.792070660717833</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ -0.1296</t>
+          <t>X ≈ -0.1295</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>165</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.008589835361491</v>
+        <v>-3.996067545685868</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.650466478628921</v>
+        <v>-8.63755666905287</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-9.045335185225369</v>
+        <v>-9.032328053807767</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.096900234436049</v>
+        <v>-7.083921092037585</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-8.847442661629564</v>
+        <v>-8.834331857254625</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.70151587542906</v>
+        <v>-3.688472979134694</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.210492016943626</v>
+        <v>-6.197425762643149</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-8.495857233906946</v>
+        <v>-8.482676224611708</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.950796514028781</v>
+        <v>-7.937597775074018</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-8.800921699056431</v>
+        <v>-8.7875165714036</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.763250780949903</v>
+        <v>-4.749793487239685</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-9.577352472089459</v>
+        <v>-9.563900183369348</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-7.573364658791661</v>
+        <v>-7.559808612440058</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.687279690151598</v>
+        <v>-3.69770932584975</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.1124</t>
+          <t>X ≈ -0.1123</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>195</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.942459115687456</v>
+        <v>4.954981405363078</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.30524447708212</v>
+        <v>2.318154286658171</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.448837308947134</v>
+        <v>3.461844440364736</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.036294173829937</v>
+        <v>-1.023315031431473</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.015028200841549</v>
+        <v>2.028139005216488</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.277273451186495</v>
+        <v>-1.26423055489213</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.874827681279285</v>
+        <v>-1.861761426978809</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2220914840417763</v>
+        <v>0.2352724933370141</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.725194161962044</v>
+        <v>2.738392900916807</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.926351028216047</v>
+        <v>3.939756155868878</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.695956678257666</v>
+        <v>2.709413971967884</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.268801374064644</v>
+        <v>4.282253662784754</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.36136727594014</v>
+        <v>4.374923322291743</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.636729633857328</v>
+        <v>5.626299998159176</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ -0.09505</t>
+          <t>X ≈ -0.09504</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>222</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.295240122011776</v>
+        <v>-4.282717832336154</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.204111032273282</v>
+        <v>-3.191201222697231</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.598979738869922</v>
+        <v>-3.585972607452319</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.072330209866074</v>
+        <v>-7.05935106746761</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-5.358499172685946</v>
+        <v>-5.345388368311006</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.259255433168484</v>
+        <v>-3.246212536874118</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.160515354063797</v>
+        <v>1.173581608364273</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.945584207534495</v>
+        <v>2.958765216829732</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.9836834204513</v>
+        <v>1.996882159406063</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.034459136324266</v>
+        <v>2.047864263977097</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.532408514709338</v>
+        <v>4.545865808419556</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.918143023406131</v>
+        <v>5.931595312126241</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.398789313362172</v>
+        <v>6.412345359713775</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.396258393386262</v>
+        <v>4.38582875768811</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.07776</t>
+          <t>X ≈ -0.07775</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>214</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.026148600583809</v>
+        <v>-2.013626310908187</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.5678852630873976</v>
+        <v>0.5807950726634488</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.042175434995592</v>
+        <v>2.055182566413194</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1640200305278157</v>
+        <v>-0.1510408881293515</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2351515259738122</v>
+        <v>-0.2220407215988729</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.293471342913655</v>
+        <v>-3.280405088613179</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.695234180947445</v>
+        <v>-4.682053171652207</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-5.690813506382078</v>
+        <v>-5.677614767427315</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.737200373653003</v>
+        <v>-3.723795246000172</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.212981735353758</v>
+        <v>-7.19952444164354</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.244019138755931</v>
+        <v>-6.230566850035821</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.196984030074724</v>
+        <v>-6.183427983723121</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.012683258546147</v>
+        <v>-5.023112894244299</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.06048</t>
+          <t>X ≈ -0.06047</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>234</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.066087892859549</v>
+        <v>-2.053565603183927</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.395610223772472</v>
+        <v>-2.382700414196421</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.354581494471724</v>
+        <v>-5.341574363054121</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.660225797761605</v>
+        <v>-2.647246655363141</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.762749576936351</v>
+        <v>-5.749638772561411</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-5.122690929142536</v>
+        <v>-5.10962467484206</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.307823045872759</v>
+        <v>-4.294642036577521</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.514122077354195</v>
+        <v>-3.500923338399431</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.372794270929134</v>
+        <v>-1.359389143276303</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2954963131954784</v>
+        <v>-0.2820390194852607</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.825215719952567</v>
+        <v>-2.811763431232457</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.390769476196617</v>
+        <v>-2.377213429845014</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.713697716569897</v>
+        <v>-1.724127352268049</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ -0.0432</t>
+          <t>X ≈ -0.04319</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>247</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.567290424729293</v>
+        <v>2.579812714404916</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.5508585121699028</v>
+        <v>0.5637683217459539</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.463443392807257</v>
+        <v>-1.450436261389655</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-2.952623458580284</v>
+        <v>-2.93964431618182</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.276469774867032</v>
+        <v>-2.263358970492092</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.979027837151371</v>
+        <v>-1.965984940857005</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8491866556382632</v>
+        <v>-0.8361204013377872</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.112779743151087</v>
+        <v>1.125960752446325</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.051779856968786</v>
+        <v>1.064978595923549</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2016546719408581</v>
+        <v>0.2150597995936891</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4079569519719115</v>
+        <v>-0.3944996582616938</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3735737946264308</v>
+        <v>-0.3601215059063207</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.3889701059761919</v>
+        <v>-0.375414059624589</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.592690069246416</v>
+        <v>-4.603119704944568</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>237</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.84411442240603</v>
+        <v>7.856636712081652</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.810599881171761</v>
+        <v>5.823509690747812</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.149908389765045</v>
+        <v>4.162915521182647</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.545984307182628</v>
+        <v>5.558963449581093</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.741740307300326</v>
+        <v>3.754851111675265</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.148886886366199</v>
+        <v>6.161929782660565</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.595798738714223</v>
+        <v>8.608864993014699</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.175028842042416</v>
+        <v>5.188209851337653</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.848206171049995</v>
+        <v>3.861404910004758</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.998080986022067</v>
+        <v>3.011486113674898</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.903032303054715</v>
+        <v>4.916489596764933</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.515474532130114</v>
+        <v>4.528926820850224</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.782983634265356</v>
+        <v>5.796539680616959</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.454645894811641</v>
+        <v>6.444216259113489</v>
       </c>
     </row>
     <row r="34">
@@ -2093,7 +2093,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-90 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-90 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2186,49 +2186,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.007183725074916936</v>
+        <v>0.006646158520375423</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02337928011300505</v>
+        <v>-0.02392596037350359</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.08116020163291182</v>
+        <v>-0.08169680352494879</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01284261235858963</v>
+        <v>0.01228367407009046</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.03880837354308397</v>
+        <v>-0.03936022861752519</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.001737825875089527</v>
+        <v>-0.002296142272783186</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02302552546516523</v>
+        <v>-0.02357967848316633</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1027033621887696</v>
+        <v>-0.103242716845287</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0003874117870736882</v>
+        <v>-0.0009531634541914968</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08861156530004166</v>
+        <v>-0.08916431284205117</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.02996128836882406</v>
+        <v>-0.03053103730391626</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.04340601094460794</v>
+        <v>0.04281803397510231</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.06145622284715557</v>
+        <v>0.06085914295810113</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.07571218567075277</v>
+        <v>0.07614098156653881</v>
       </c>
     </row>
     <row r="7">
@@ -2238,49 +2238,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.07912758716018686</v>
+        <v>-0.07971543023420935</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.000907829070129651</v>
+        <v>-0.001534197653725755</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05682682249923232</v>
+        <v>-0.05744407892378689</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.01309270496001602</v>
+        <v>-0.01371970393883259</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.06206825642031077</v>
+        <v>-0.06268954530171555</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05148854804688341</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0473825965052157</v>
+        <v>-0.04800571041748469</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1499925722528062</v>
+        <v>-0.1505957101207684</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.04678776268972484</v>
+        <v>-0.04741777963072735</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1809709376815363</v>
+        <v>-0.181577511716867</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.145971897305337</v>
+        <v>-0.146589937195607</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04733072932297233</v>
+        <v>-0.04797342139278982</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.001789433515185124</v>
+        <v>-0.002448762054754638</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.01115039382037963</v>
+        <v>0.0116553370905379</v>
       </c>
     </row>
     <row r="8">
@@ -2290,101 +2290,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3947</v>
+        <v>3948</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.09444842122007202</v>
+        <v>-0.09515485911298782</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.000440071593025948</v>
+        <v>-0.001193032689094764</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.02792510667329395</v>
+        <v>-0.02867699408193403</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1113510350885178</v>
+        <v>-0.1120804011468763</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1304956383123326</v>
+        <v>-0.1312280366374097</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.09733244823664222</v>
+        <v>-0.09806944939836626</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.04182507437683114</v>
+        <v>-0.04257766089239112</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1157240017625796</v>
+        <v>-0.1164647931498948</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01097317946846488</v>
+        <v>-0.01174169338678155</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2396828872482786</v>
+        <v>-0.2404057874508467</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2530858404052125</v>
+        <v>-0.2538085812320006</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1285468672948582</v>
+        <v>-0.1293010272510671</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.07866078110919972</v>
+        <v>-0.07943383401527626</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.04262437080691939</v>
+        <v>-0.04200332971850429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.4493</t>
+          <t>X &gt; -0.4492</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3904</v>
+        <v>3905</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1829966556707916</v>
+        <v>-0.1838256783138306</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1213551405286779</v>
+        <v>-0.1222272193347109</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1448359398985346</v>
+        <v>-0.1457090548292186</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1795406395087511</v>
+        <v>-0.1804031540368882</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2441080117831476</v>
+        <v>-0.2449634671707202</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2650035125361896</v>
+        <v>-0.2658490913943865</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1568592949396503</v>
+        <v>-0.1577343701910223</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1497361767884513</v>
+        <v>-0.1506213366887579</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.171080706684279</v>
+        <v>-0.1719618764456499</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3674053689179289</v>
+        <v>-0.3682510070882827</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.404330117959617</v>
+        <v>-0.4051701815109539</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3044390056274722</v>
+        <v>-0.3053045004070114</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2750291914422434</v>
+        <v>-0.2759097156380719</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2157819256213287</v>
+        <v>-0.2149948572200628</v>
       </c>
     </row>
     <row r="10">
@@ -2394,49 +2394,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3865</v>
+        <v>3866</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.09529494733735788</v>
+        <v>-0.09628081527268506</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01679939770866667</v>
+        <v>-0.01783703850277618</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.01508324051813759</v>
+        <v>0.01402925151266032</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.04704686200203412</v>
+        <v>-0.0480828332891079</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.08099657974710794</v>
+        <v>-0.0820346920541013</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.05341597636078177</v>
+        <v>-0.05445598941287244</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.005072721348390985</v>
+        <v>0.004015450416964939</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1203487421543628</v>
+        <v>0.1192521500439412</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.04779404270145449</v>
+        <v>0.04671447686947516</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.09019071383604427</v>
+        <v>-0.09125159606900013</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1253516239194141</v>
+        <v>-0.1264079127039466</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.02699198097507605</v>
+        <v>0.02589643848531864</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0610237153792923</v>
+        <v>0.05991069075466982</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.04081627597772552</v>
+        <v>0.04165012483896646</v>
       </c>
     </row>
     <row r="11">
@@ -2446,49 +2446,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3823</v>
+        <v>3824</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1472443681766009</v>
+        <v>-0.1483645580297903</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08012496382707468</v>
+        <v>0.07890934668336058</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.01370432260858223</v>
+        <v>-0.01490479909637088</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.02640693061387367</v>
+        <v>0.0251982706028997</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.07629365772275776</v>
+        <v>0.07505947321693185</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1792653115386358</v>
+        <v>0.1780102245093929</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1088370438997899</v>
+        <v>0.107597848566833</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2305291158797758</v>
+        <v>0.2292471870506105</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1056298182597573</v>
+        <v>0.104378530156545</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.0245243310731027</v>
+        <v>-0.02576108551032519</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.05780637346681061</v>
+        <v>-0.0590395934546919</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.06970635144008952</v>
+        <v>0.06843994557311106</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2133413130606243</v>
+        <v>0.212027394689926</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1902082417435906</v>
+        <v>0.1911267334881188</v>
       </c>
     </row>
     <row r="12">
@@ -2498,153 +2498,153 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3788</v>
+        <v>3789</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.01905839118176544</v>
+        <v>0.01776887214845146</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3160406984047128</v>
+        <v>0.3146329461203123</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1987242562544509</v>
+        <v>0.1973370179625675</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2117311026313047</v>
+        <v>0.210342948738699</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.2407529633057237</v>
+        <v>0.2393432827713511</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4210054388732161</v>
+        <v>0.4195548897571584</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3507728051907577</v>
+        <v>0.3493379759014132</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5570332949983481</v>
+        <v>0.5555319440312445</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3525373785486039</v>
+        <v>0.3510877091835596</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2027223362330446</v>
+        <v>0.2012905613527707</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1183267991241195</v>
+        <v>0.1169115376931842</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1939755841991513</v>
+        <v>0.1925405094998638</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.369244328947822</v>
+        <v>0.3677519536428022</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3436313206957777</v>
+        <v>0.3446141464021863</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.3802</t>
+          <t>X &gt; -0.3801</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3751</v>
+        <v>3752</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.04923003115577984</v>
+        <v>-0.05063714607219794</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.266500158242188</v>
+        <v>0.2649648264549569</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2316451443865404</v>
+        <v>0.2301076237222475</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.243507297409927</v>
+        <v>0.2419693917476309</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3047172352113137</v>
+        <v>0.303147697667228</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4838332261212983</v>
+        <v>0.4822233458170899</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4137600836256681</v>
+        <v>0.4121657631494955</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6000526232485797</v>
+        <v>0.5983952673166257</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4207786626583641</v>
+        <v>0.4191665678496364</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2778823198273486</v>
+        <v>0.2762843773812449</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1680548163120079</v>
+        <v>0.166479764586164</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2707690307084363</v>
+        <v>0.2691667674388114</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5851932012586047</v>
+        <v>0.5834949265467984</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5835814135538016</v>
+        <v>0.5846128296064563</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.3629</t>
+          <t>X &gt; -0.3628</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3702</v>
+        <v>3703</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1919578356877665</v>
+        <v>-0.1935102178325252</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2299369090444046</v>
+        <v>0.2282208912066679</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.09209350512548298</v>
+        <v>0.09040166666024163</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1831742169746136</v>
+        <v>0.1814609807778282</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.198391590348713</v>
+        <v>0.1966569097256539</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3489619486338071</v>
+        <v>0.3471949368890606</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3060075704645655</v>
+        <v>0.3042486635595836</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4200003712710441</v>
+        <v>0.4181955287809416</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2930664479352103</v>
+        <v>0.2912930751761991</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.159486484233426</v>
+        <v>0.1577221661198678</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.07787300754230131</v>
+        <v>0.07612353511554204</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2624603428854826</v>
+        <v>0.2606612201395606</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5595987860809046</v>
+        <v>0.5577056227846171</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.527640991543521</v>
+        <v>0.5288391729101889</v>
       </c>
     </row>
     <row r="15">
@@ -2654,49 +2654,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3646</v>
+        <v>3647</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1840641742684639</v>
+        <v>-0.1858340633212308</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3236376020909404</v>
+        <v>0.3216721316628224</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1897556741476905</v>
+        <v>0.1878121122044618</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2255584884603081</v>
+        <v>0.2236086765258207</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.08511133248406821</v>
+        <v>0.08318024406505486</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2333997836246695</v>
+        <v>0.2314374797635921</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1910542422538768</v>
+        <v>0.1890995893994472</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2591628464143412</v>
+        <v>0.2571723017136804</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1311735564377372</v>
+        <v>0.1292149302930525</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.09073458985999849</v>
+        <v>0.08875642976655485</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.03839682694599134</v>
+        <v>0.03642486062249617</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3623405103668205</v>
+        <v>0.3602799573085989</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5334229873432577</v>
+        <v>0.5312998405103642</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5245589374848834</v>
+        <v>0.5259365100798803</v>
       </c>
     </row>
     <row r="16">
@@ -2706,49 +2706,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3595</v>
+        <v>3596</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08213011621884192</v>
+        <v>-0.08413021728969028</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2337737613087185</v>
+        <v>0.2316229318341883</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1867527490256222</v>
+        <v>0.1845986291571791</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1380007868727375</v>
+        <v>0.1358641144364654</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.03090799252588283</v>
+        <v>0.02877914177883412</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2325794491743096</v>
+        <v>0.230405035192959</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3018832627831216</v>
+        <v>0.2996852307209679</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2665235862356141</v>
+        <v>0.2643161870114596</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1375873243552022</v>
+        <v>0.1354122473946262</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2475513616421097</v>
+        <v>0.2453117114245416</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1974176038429931</v>
+        <v>0.195182810890266</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3865062991089019</v>
+        <v>0.3842191421820189</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6215994427351532</v>
+        <v>0.6192294748547766</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5812751208229656</v>
+        <v>0.5828043762432031</v>
       </c>
     </row>
     <row r="17">
@@ -2758,101 +2758,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3524</v>
+        <v>3525</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1044080685843056</v>
+        <v>-0.1066933058311292</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3633138586809679</v>
+        <v>0.3608240850532169</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2101617930438877</v>
+        <v>0.2076966273933891</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1295235964020449</v>
+        <v>0.1270857229296212</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.03109648014208943</v>
+        <v>0.02866140302230491</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2591553898856063</v>
+        <v>0.2566676430510668</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3882052359592407</v>
+        <v>0.3856759223837898</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3898840314377168</v>
+        <v>0.3873322715650147</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2596159128757094</v>
+        <v>0.2570970485161297</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2188680350188861</v>
+        <v>0.2163217551889076</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1434859942303035</v>
+        <v>0.1409506892187764</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3356745651577953</v>
+        <v>0.3330849787137709</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5555844063274762</v>
+        <v>0.5529124724873498</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5377744838239806</v>
+        <v>0.5395569539694449</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.2938</t>
+          <t>X &gt; -0.2937</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3440</v>
+        <v>3441</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.06955038526352553</v>
+        <v>0.06685467010259316</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.41410741792658</v>
+        <v>0.4112283137027219</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2088994239788207</v>
+        <v>0.2060581254822438</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1521116232714661</v>
+        <v>0.1492919423924803</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.05156858306472145</v>
+        <v>-0.05435820771562305</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1167714057353848</v>
+        <v>0.1139466945521477</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3960433102183316</v>
+        <v>0.3931317849909632</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.4671917117305071</v>
+        <v>0.4642341322203194</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1610915978594747</v>
+        <v>0.1582181907362923</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1981280317004845</v>
+        <v>0.1951988264060063</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.009718528760622291</v>
+        <v>0.006832001093123097</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.089507880418914</v>
+        <v>0.08659841281628644</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3830962008948688</v>
+        <v>0.3800783454595447</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1842847918777224</v>
+        <v>0.1864681067145071</v>
       </c>
     </row>
     <row r="19">
@@ -2862,49 +2862,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1179514702887019</v>
+        <v>0.1149541759553259</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4372575695266292</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2978754865946911</v>
+        <v>0.2947085459561123</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2080452630670351</v>
+        <v>0.2049105369180495</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.06979470464781912</v>
+        <v>0.06666869761493643</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2948305677260379</v>
+        <v>0.2916532461910819</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6106009702740991</v>
+        <v>0.6073238612554093</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6624317469722172</v>
+        <v>0.6591111436019119</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3517498009400413</v>
+        <v>0.3485158747298982</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3168835725948611</v>
+        <v>0.313610045250833</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.1584133298234107</v>
+        <v>0.155173340804069</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.2687102869396867</v>
+        <v>0.265437885092858</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5758802331241029</v>
+        <v>0.5724912960586508</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3390020849450579</v>
+        <v>0.3413786220327069</v>
       </c>
     </row>
     <row r="20">
@@ -2917,46 +2917,46 @@
         <v>3278</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1081450962658934</v>
+        <v>-0.1260087075322218</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2718877628743996</v>
+        <v>0.2544024356723327</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.07597828391418204</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1011754125447055</v>
+        <v>0.08374092963903479</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.08602255856040841</v>
+        <v>-0.1033346321897355</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1976707565635536</v>
+        <v>0.1802815165219513</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4644768498060614</v>
+        <v>0.4471017038021259</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5622020433971571</v>
+        <v>0.5449323827776524</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2744963168079053</v>
+        <v>0.2572351105905639</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3248885053642425</v>
+        <v>0.307824406935417</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1373246164252464</v>
+        <v>0.1203033974868859</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.1889076905123019</v>
+        <v>0.202359979232412</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.487296851092033</v>
+        <v>0.5008528974436359</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.3883761975845488</v>
+        <v>0.3779465618863966</v>
       </c>
     </row>
     <row r="21">
@@ -2969,46 +2969,46 @@
         <v>3125</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2141906313352564</v>
+        <v>-0.2183283950977639</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2317227607033203</v>
+        <v>0.2273113287448183</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.08201780085535404</v>
+        <v>-0.08636330427158612</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2215739015474938</v>
+        <v>-0.2258668655623097</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4554473816673479</v>
+        <v>-0.4597113703174713</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.07676259550323294</v>
+        <v>-0.08112596929792204</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.0794918201497623</v>
+        <v>0.07506930295537018</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1729393582123322</v>
+        <v>0.168446952222105</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1260485550524919</v>
+        <v>-0.1304528433282997</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.06341879275571216</v>
+        <v>-0.06791402629783505</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3781784393697265</v>
+        <v>-0.38259206121473</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3259129327419146</v>
+        <v>-0.3303429933041855</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.07172625029910762</v>
+        <v>0.0671325845585784</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1265524174245982</v>
+        <v>-0.1369820531227504</v>
       </c>
     </row>
     <row r="22">
@@ -3021,98 +3021,98 @@
         <v>2978</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.03587491262084797</v>
+        <v>0.04839720229647071</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.3856046888096785</v>
+        <v>0.3802596854470437</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.09127217524257958</v>
+        <v>0.1042793066601817</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1289302225505153</v>
+        <v>-0.1341282575262568</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3656417493893684</v>
+        <v>-0.3525309450144292</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.06589338309666459</v>
+        <v>0.07893627939102998</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1000988006894445</v>
+        <v>0.09479581620263389</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.2215753949648018</v>
+        <v>0.2161836010086802</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1228526458163159</v>
+        <v>-0.1281378622929381</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1532728140503323</v>
+        <v>0.1478098471441669</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1669180785057236</v>
+        <v>-0.1722964626127563</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1325349211602926</v>
+        <v>-0.1190826324401826</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.2867000582238859</v>
+        <v>0.3002561045754888</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.09988680352905988</v>
+        <v>0.08945716783090774</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.2074</t>
+          <t>X &gt; -0.2073</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2790</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1739444223607336</v>
+        <v>0.1864667120363563</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1019340030950175</v>
+        <v>0.1148438126710687</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.02929945331904804</v>
+        <v>0.04230658473665017</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1626815708940725</v>
+        <v>-0.1497024284956083</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1282420627295906</v>
+        <v>-0.1151312583546513</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.009819101025385635</v>
+        <v>0.003223795268979757</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1202699529160896</v>
+        <v>0.1333362072165656</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.03088584154673413</v>
+        <v>0.02430551545273829</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1894858075369896</v>
+        <v>-0.1959984002366753</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1629101680011047</v>
+        <v>0.1561660447976863</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2210546258505204</v>
+        <v>-0.2075973321403026</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.04330229287784704</v>
+        <v>-0.02985000415773698</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1816043864998207</v>
+        <v>0.1951604328514236</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.1804296614284482</v>
+        <v>0.170000025730296</v>
       </c>
     </row>
     <row r="24">
@@ -3125,46 +3125,46 @@
         <v>2621</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4252949876877707</v>
+        <v>0.4378172773633935</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.5687766971195529</v>
+        <v>0.5816865066956041</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4028282499659213</v>
+        <v>0.4158353813835234</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2278543699828006</v>
+        <v>0.2408335123812648</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.338040556665689</v>
+        <v>0.3511513610406283</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4065622349383915</v>
+        <v>0.4196051312327569</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5507487771090709</v>
+        <v>0.5638150314095469</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.3506390143443596</v>
+        <v>0.3638200236395974</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.2514857515882341</v>
+        <v>0.2646844905429973</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5459618637751049</v>
+        <v>0.559366991427936</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1885950331622155</v>
+        <v>0.2020523268724332</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.4137450733767878</v>
+        <v>0.4271973620968978</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8710181236298951</v>
+        <v>0.884574169981498</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8918191964632314</v>
+        <v>0.8813895607650792</v>
       </c>
     </row>
     <row r="25">
@@ -3174,49 +3174,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.016389196837764</v>
+        <v>1.050384129979285</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.169757421017501</v>
+        <v>1.20484811717229</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.09578723026528</v>
+        <v>1.131104019736668</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.7848049035867746</v>
+        <v>0.819916643260818</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.682911199314411</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.7443871986329924</v>
+        <v>0.7796431743748542</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.9805519972050831</v>
+        <v>1.015960102428103</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.7941547997873997</v>
+        <v>0.829790335045864</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6930425991245528</v>
+        <v>0.7286797676081633</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.006174534032446</v>
+        <v>1.042484887811213</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.6810842662732313</v>
+        <v>0.7173984968062257</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.7956920525797528</v>
+        <v>0.8320334709914121</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.217796045726303</v>
+        <v>1.254579246891481</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.18673117663878</v>
+        <v>1.159287609798596</v>
       </c>
     </row>
     <row r="26">
@@ -3229,46 +3229,46 @@
         <v>2333</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.8713280749893357</v>
+        <v>0.8838503646649585</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.145738173983929</v>
+        <v>1.15864798355998</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.093775596834405</v>
+        <v>1.106782728252007</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6239430029095416</v>
+        <v>0.6369221453080058</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.5570177158270937</v>
+        <v>0.570128520202033</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8115963873618668</v>
+        <v>0.8246392836562322</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.155495331898415</v>
+        <v>1.168561586198891</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.07408132874486</v>
+        <v>1.087262338040098</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.098807974924334</v>
+        <v>1.112006713879097</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.534580775322894</v>
+        <v>1.547985902975725</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.286964184824434</v>
+        <v>1.300421478534652</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.664253471616924</v>
+        <v>1.677705760337034</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.186990716651451</v>
+        <v>2.200546763003054</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.179532451842434</v>
+        <v>2.169102816144282</v>
       </c>
     </row>
     <row r="27">
@@ -3281,98 +3281,98 @@
         <v>2175</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.161734093583128</v>
+        <v>1.174256383258751</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.929470825446451</v>
+        <v>0.9423806350225021</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.5805791303441197</v>
+        <v>0.5935862617617218</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1591081250205875</v>
+        <v>0.1720872674190517</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.01149699809756299</v>
+        <v>0.001613806277376284</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4238759741008522</v>
+        <v>0.4369188703952176</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.166728463725129</v>
+        <v>1.179794718025605</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.34322322586317</v>
+        <v>1.356404235158408</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.466131385657874</v>
+        <v>1.479330124612638</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.903362522469031</v>
+        <v>1.916767650121862</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.744586209645711</v>
+        <v>1.758043503355928</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.238739481933671</v>
+        <v>2.252191770653781</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.692048089379576</v>
+        <v>2.705604135731178</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.75786137567885</v>
+        <v>2.747431739980698</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.121</t>
+          <t>X &gt; -0.1209</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2010</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.586163669839777</v>
+        <v>1.5986859595154</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.715883589213824</v>
+        <v>1.728793398789875</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.37076612639833</v>
+        <v>1.383773257815932</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7547506022894126</v>
+        <v>0.7677297446878768</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.7138418250281973</v>
+        <v>0.7269526294031365</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.762527543838381</v>
+        <v>0.7755704401327463</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.77232118975018</v>
+        <v>1.785387444050656</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.150908935247287</v>
+        <v>2.164089944542525</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.239162780408265</v>
+        <v>2.252361519363028</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.78207242125098</v>
+        <v>2.795477548903811</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.278811634246843</v>
+        <v>2.29226892795706</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.208717179651977</v>
+        <v>3.222169468372087</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.534731225423492</v>
+        <v>3.548287271775095</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.286940119888826</v>
+        <v>3.276510484190673</v>
       </c>
     </row>
     <row r="29">
@@ -3385,202 +3385,202 @@
         <v>1815</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.225569944252832</v>
+        <v>1.238092233928455</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.652563824401533</v>
+        <v>1.665473633977584</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.147502280339367</v>
+        <v>1.160509411756969</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.9471769005501685</v>
+        <v>0.9601560429486327</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.5740449416763553</v>
+        <v>0.5871557460512946</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.9816797168575775</v>
+        <v>0.9947226131519429</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.164163630439297</v>
+        <v>2.177229884739774</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.35813725645118</v>
+        <v>2.371318265746417</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.186944532803317</v>
+        <v>2.20014327175808</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.659133397362169</v>
+        <v>2.672538525015</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.233994398113452</v>
+        <v>2.24745169182367</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.094823836450622</v>
+        <v>3.108276125170732</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.445919087764672</v>
+        <v>3.459475134116275</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.034483395247577</v>
+        <v>3.024053759549425</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; -0.0864</t>
+          <t>X &gt; -0.08639</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1593</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.994948371566551</v>
+        <v>2.007470661242174</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.329388569022882</v>
+        <v>2.342298378598933</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.808970584334638</v>
+        <v>1.82197771575224</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.064772995033792</v>
+        <v>2.077752137432256</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.400802501869968</v>
+        <v>1.413913306244908</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.572695161493975</v>
+        <v>1.58573805778834</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.304031751817426</v>
+        <v>2.317098006117902</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.276270826356708</v>
+        <v>2.289451835651946</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.215270940174406</v>
+        <v>2.228469679129169</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.746187814154645</v>
+        <v>2.759592941807476</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.913688099378803</v>
+        <v>1.92714539308902</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.701366925274151</v>
+        <v>2.714819213994261</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.034407982879152</v>
+        <v>3.047964029230755</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.84470684183465</v>
+        <v>2.834277206136498</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.06912</t>
+          <t>X &gt; -0.06911</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1379</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.618961969855292</v>
+        <v>2.631484259530914</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.602747312656085</v>
+        <v>2.615657122232136</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.772780709032652</v>
+        <v>1.785787840450254</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.410648054838127</v>
+        <v>2.423627197236591</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.65467789125254</v>
+        <v>1.667788695627479</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.172679802776415</v>
+        <v>3.185746057076891</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.358143249535161</v>
+        <v>3.371324258830398</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.442175995695138</v>
+        <v>3.455374734649901</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.752311869405425</v>
+        <v>3.765716997058256</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.330009596574428</v>
+        <v>3.343466890284645</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.089555915631244</v>
+        <v>4.103008204351354</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.466980782568875</v>
+        <v>4.480536828920478</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.064055269304909</v>
+        <v>4.053625633606757</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.05184</t>
+          <t>X &gt; -0.05183</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.576430675423211</v>
+        <v>3.588952965098834</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.624245708747161</v>
+        <v>3.637155518323212</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.229377002150571</v>
+        <v>3.242384133568173</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.44696637929956</v>
+        <v>3.459945521698025</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.170553897851846</v>
+        <v>3.183664702226785</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.99201330281641</v>
+        <v>4.005056199110776</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.867978275500462</v>
+        <v>4.881044529800938</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.924812343967879</v>
+        <v>4.937993353263117</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.863812457785578</v>
+        <v>4.877011196740341</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.799713473631009</v>
+        <v>4.81311860128384</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.070942682064526</v>
+        <v>4.084399975774744</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.502705752073709</v>
+        <v>5.516158040793819</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.868477342002166</v>
+        <v>5.882033388353769</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.244836228863605</v>
+        <v>5.234406593165453</v>
       </c>
     </row>
     <row r="33">
@@ -3593,46 +3593,46 @@
         <v>898</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.85400043257399</v>
+        <v>3.866522722249613</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.469598311814636</v>
+        <v>4.482508121390687</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.520163903659018</v>
+        <v>4.53317103507662</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.20720990931774</v>
+        <v>5.220189051716204</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.668788694245571</v>
+        <v>4.68189949862051</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.634382079622704</v>
+        <v>5.647424975917069</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.44051695923239</v>
+        <v>6.453583213532866</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.973333560450889</v>
+        <v>5.986514569746127</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.912333674268588</v>
+        <v>5.925532413223351</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.064435660732862</v>
+        <v>6.077840788385693</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.302889463364068</v>
+        <v>5.316346757074285</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.119009814473408</v>
+        <v>7.132462103193518</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.589623800410472</v>
+        <v>7.603179846762075</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.950703707296995</v>
+        <v>7.940274071598843</v>
       </c>
     </row>
     <row r="34">
@@ -3645,46 +3645,46 @@
         <v>661</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.423354418065372</v>
+        <v>2.435876707740995</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.988785343679019</v>
+        <v>4.001695153255071</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.652918149941733</v>
+        <v>4.665925281359335</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.08574314336618</v>
+        <v>5.098722285764644</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.001179719519421</v>
+        <v>5.01429052389436</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.449907587643558</v>
+        <v>5.462950483937924</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.667745731188226</v>
+        <v>5.680811985488702</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.25956384526603</v>
+        <v>6.272744854561267</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.652421750309145</v>
+        <v>6.665620489263908</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.163869938957461</v>
+        <v>7.177275066610292</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.446257310555168</v>
+        <v>5.459714604265386</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.05250128484461</v>
+        <v>8.06595357356472</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.237390395533602</v>
+        <v>8.250946441885205</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.487111727809889</v>
+        <v>8.476682092111737</v>
       </c>
     </row>
     <row r="35">
@@ -3759,7 +3759,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-90 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-90 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3855,46 +3855,46 @@
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.723429149669542</v>
+        <v>1.735951439345165</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.726313368030581</v>
+        <v>3.739223177606632</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.126625384325571</v>
+        <v>2.139632515743173</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.461697794041491</v>
+        <v>3.474676936439955</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.537734410294625</v>
+        <v>6.550845214669565</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.425537793793424</v>
+        <v>4.43858069008779</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.135984799412704</v>
+        <v>3.14905105371318</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.078439954848079</v>
+        <v>5.091620964143317</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.812620791557343</v>
+        <v>3.825819530512106</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.576953437854719</v>
+        <v>6.59035856550755</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.167380836428698</v>
+        <v>5.180838130138916</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.996944716665702</v>
+        <v>4.010397005385812</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.19114793704609</v>
+        <v>7.204703983397692</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.440869269322377</v>
+        <v>7.430439633624225</v>
       </c>
     </row>
     <row r="7">
@@ -3907,46 +3907,46 @@
         <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.085464257301958</v>
+        <v>2.098374066878009</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7382145983244186</v>
+        <v>0.7512217297420207</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.72561058807478</v>
+        <v>3.738589730473244</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.044332230145464</v>
+        <v>6.057443034520404</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.402436111774534</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.399897593445992</v>
+        <v>3.412963847746468</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.789857051807346</v>
+        <v>5.803038061102583</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.68825579012092</v>
+        <v>8.701660917773751</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.48350246580334</v>
+        <v>8.496959759513558</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.613123718386866</v>
+        <v>6.626576007106976</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.09763101220387</v>
+        <v>8.111187058555473</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.347352344480157</v>
+        <v>8.336922708782005</v>
       </c>
     </row>
     <row r="8">
@@ -3959,98 +3959,98 @@
         <v>142</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.844589848804112</v>
+        <v>3.857112138479735</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.528790883727183</v>
+        <v>1.541700693303234</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2745285270947591</v>
+        <v>-0.2615213956771569</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.489527422414142</v>
+        <v>5.502506564812606</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.359556911567324</v>
+        <v>6.372667715942264</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.248548145057633</v>
+        <v>5.261591041351998</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.34691301933465</v>
+        <v>2.359979273635126</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.288180324778502</v>
+        <v>3.301361334073739</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.522955086483528</v>
+        <v>2.536153825438291</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.010858070469681</v>
+        <v>8.024263198122512</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.21455545037746</v>
+        <v>9.228012744087678</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.13626255138486</v>
+        <v>7.14971484010497</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.124458644665317</v>
+        <v>8.13801469101692</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.669954624828918</v>
+        <v>7.659524989130766</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.4493</t>
+          <t>X &lt; -0.4492</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>185</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.803858977087323</v>
+        <v>4.816381266762946</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.732825904663606</v>
+        <v>3.745735714239657</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.256876116985936</v>
+        <v>2.269883248403538</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.25411343992667</v>
+        <v>7.267224244301609</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.55155537764233</v>
+        <v>7.564598273936696</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.223578417126809</v>
+        <v>4.236644671427285</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.215854477804768</v>
+        <v>3.229035487100006</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.317016753784635</v>
+        <v>5.330215492739399</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.791215893081031</v>
+        <v>8.804621020733862</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>10.20808419038507</v>
+        <v>10.22154148409528</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.161386266649416</v>
+        <v>9.174838555369526</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>10.36275327732614</v>
+        <v>10.37630932367775</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.531393528521349</v>
+        <v>9.520963892823197</v>
       </c>
     </row>
     <row r="10">
@@ -4063,46 +4063,46 @@
         <v>224</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.417275965504317</v>
+        <v>2.429798255179939</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.252130923968629</v>
+        <v>1.26504073354468</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.9284520683422528</v>
+        <v>-0.9154449369246507</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.326801064265247</v>
+        <v>2.339780206663711</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.1276655634788</v>
+        <v>3.140776367853739</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.6618023553507513</v>
+        <v>0.6748686096512273</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.037523900573611</v>
+        <v>-2.024342891278373</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5800476418155185</v>
+        <v>0.5932463807702817</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.408493885359022</v>
+        <v>2.421899013011853</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.543026275327151</v>
+        <v>3.556483569037368</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.791695146958304</v>
+        <v>1.805147435678414</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.710726250299111</v>
+        <v>2.724282296650713</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.406876154003967</v>
+        <v>3.396446518305815</v>
       </c>
     </row>
     <row r="11">
@@ -4115,46 +4115,46 @@
         <v>266</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.769719574526874</v>
+        <v>2.782241864202497</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3456134369336255</v>
+        <v>-0.3327036273575743</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3645422939061618</v>
+        <v>-0.3515351624885596</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.8935303875735272</v>
+        <v>0.9065095299719914</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.3551091725013578</v>
+        <v>0.368219976876297</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.227148137903285</v>
+        <v>-1.21410524160892</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.9359420055515031</v>
+        <v>-0.9228757512510271</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.282824652453307</v>
+        <v>-3.269643643158069</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3363057416431303</v>
+        <v>-0.3231070026883671</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.992274395627909</v>
+        <v>2.005731689338127</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1026435435321957</v>
+        <v>0.1161995898837986</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="12">
@@ -4167,150 +4167,150 @@
         <v>301</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3304819455707602</v>
+        <v>0.3430042352463829</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.274447149121073</v>
+        <v>-3.261537339545022</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.00486402847514</v>
+        <v>-2.991856897057538</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.545707241382587</v>
+        <v>-1.532728098984123</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.751902542833491</v>
+        <v>-1.738791738458552</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.112267914087937</v>
+        <v>-4.099225017793572</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.864775717738951</v>
+        <v>-3.851709463438475</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.989766425490558</v>
+        <v>-6.97658541619532</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.396281261838972</v>
+        <v>-3.383082522884209</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.920825051518058</v>
+        <v>-1.907419923865227</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4644488077293261</v>
+        <v>-0.4509915140191083</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7622915640051602</v>
+        <v>-0.7488392752850501</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.846998002192578</v>
+        <v>-1.833441955840975</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.265050756295039</v>
+        <v>-1.275480391993192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.3802</t>
+          <t>X &lt; -0.3801</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>338</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.056857537778185</v>
+        <v>1.069379827453808</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.329864004180152</v>
+        <v>-2.316954194604101</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.020590698942421</v>
+        <v>-3.007583567524819</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.706905613672198</v>
+        <v>-1.693926471273734</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.245326828744368</v>
+        <v>-2.232216024369428</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.314748796354152</v>
+        <v>-4.301705900059787</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.103624525460745</v>
+        <v>-4.090558271160269</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.641813841402012</v>
+        <v>-6.628632832106774</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.744233845927511</v>
+        <v>-3.731035106972747</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.523353113795679</v>
+        <v>-2.509947986142848</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.9529585091191635</v>
+        <v>-0.9395012154089457</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.510291328105097</v>
+        <v>-1.496839039384987</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.001551856209765</v>
+        <v>-3.987995809858162</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.751830523933478</v>
+        <v>-3.76226015963163</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.3629</t>
+          <t>X &lt; -0.3628</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>387</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.286923436895968</v>
+        <v>2.299445726571591</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.65023157141713</v>
+        <v>-1.637321761841079</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.269906479564106</v>
+        <v>-1.256899348146504</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.881255414140071</v>
+        <v>-0.8682762717416068</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.9028807635791622</v>
+        <v>-0.889769959204223</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.414224355579265</v>
+        <v>-2.401181459284899</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.498958072851543</v>
+        <v>-2.485891818551067</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.999733202899186</v>
+        <v>-3.986552193603949</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.993549626549196</v>
+        <v>-1.980350887594433</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.034889281861361</v>
+        <v>-1.02148415420853</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.05234705790375216</v>
+        <v>0.06580435161396991</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.205259448833509</v>
+        <v>-1.191807160113399</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.175901656677638</v>
+        <v>-3.162345610326035</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.667782391584808</v>
+        <v>-2.67821202728296</v>
       </c>
     </row>
     <row r="15">
@@ -4323,46 +4323,46 @@
         <v>443</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.908367548864518</v>
+        <v>1.920889838540141</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.186276041526369</v>
+        <v>-2.173366231950318</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.903943845188437</v>
+        <v>-1.890936713770834</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.0964898096464</v>
+        <v>-1.083510667247936</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1709580497735388</v>
+        <v>0.1840688541484781</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.111735452691384</v>
+        <v>-1.098692556397019</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.196469169963663</v>
+        <v>-1.183402915663187</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.115119837368191</v>
+        <v>-2.101938828072953</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3702506490583914</v>
+        <v>-0.3570519101036282</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.317441296840272</v>
+        <v>-0.3040361691874409</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3807399160881957</v>
+        <v>0.3941972097984134</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.842213269681494</v>
+        <v>-1.828760980961384</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.488201514937906</v>
+        <v>-2.474645468586303</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.238480182661618</v>
+        <v>-2.24890981835977</v>
       </c>
     </row>
     <row r="16">
@@ -4375,46 +4375,46 @@
         <v>494</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9478572263487308</v>
+        <v>0.9603795160243536</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.271003836008234</v>
+        <v>-1.258094026432182</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.665872542604824</v>
+        <v>-1.652865411187221</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3210445112119018</v>
+        <v>-0.3080653688134376</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5575383222989245</v>
+        <v>0.5706491266738638</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9668820881635583</v>
+        <v>-0.9538391918691929</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.861332404626111</v>
+        <v>-1.848266150325635</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.923657503812478</v>
+        <v>-1.910476494517241</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3652241916142103</v>
+        <v>-0.3520254526594471</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.417778526439704</v>
+        <v>-1.404373398786873</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8128152515670024</v>
+        <v>-0.7993579578567847</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.790577843209434</v>
+        <v>-1.777125554489324</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.818119903547043</v>
+        <v>-2.80456385719544</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.365969421473181</v>
+        <v>-2.376399057171334</v>
       </c>
     </row>
     <row r="17">
@@ -4427,98 +4427,98 @@
         <v>565</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9578891134183394</v>
+        <v>0.9704114030939621</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.892622552643253</v>
+        <v>-1.879712743067202</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.579526657469941</v>
+        <v>-1.566519526052339</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2103354717650916</v>
+        <v>-0.1973563293666274</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4901813662600816</v>
+        <v>0.5032921706350209</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.9822882004490339</v>
+        <v>-0.9692453041546685</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.128968820376187</v>
+        <v>-2.115902566075711</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.419161068715205</v>
+        <v>-2.405980059419967</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.064231751357681</v>
+        <v>-1.051033012402918</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.029401184173217</v>
+        <v>-1.015996056520386</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3491987562784047</v>
+        <v>-0.3357414625681869</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.199771351145365</v>
+        <v>-1.186319062425255</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.974008262975225</v>
+        <v>-1.960452216623622</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.724286930698938</v>
+        <v>-1.73471656639709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.2938</t>
+          <t>X &lt; -0.2937</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>649</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1051486437847018</v>
+        <v>-0.09262635410907905</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.87080546167963</v>
+        <v>-1.857895652103579</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.341174938692241</v>
+        <v>-1.328167807274639</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2864225765007689</v>
+        <v>-0.2734434341023046</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.870071462664356</v>
+        <v>0.8831822670392953</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.84480121057485</v>
+        <v>-1.831734956274374</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.466067814287022</v>
+        <v>-2.452886804991785</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3699028314400366</v>
+        <v>-0.3567040924852733</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7577784016759779</v>
+        <v>-0.7443732740231468</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4242171183824013</v>
+        <v>0.437674412092619</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3045170707971678</v>
+        <v>0.3179693595172779</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7320703598703844</v>
+        <v>-0.7185143135187815</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4421502019898753</v>
+        <v>0.4317205662917232</v>
       </c>
     </row>
     <row r="19">
@@ -4531,46 +4531,46 @@
         <v>713</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3070029870560944</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.79084643527802</v>
+        <v>-1.777936625701969</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.6247053242028</v>
+        <v>-1.611698192785198</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5126850106696352</v>
+        <v>-0.499705868271171</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.2111658640197689</v>
+        <v>0.2242766683947082</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8939167424440981</v>
+        <v>-0.8808738461497327</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.661679912731806</v>
+        <v>-2.64861365843133</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.128863311513307</v>
+        <v>-3.115682302218069</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.226328835844271</v>
+        <v>-1.213130096889508</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.234939294364487</v>
+        <v>-1.221534166711656</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3176729833384471</v>
+        <v>-0.3042156896282293</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5637947348289174</v>
+        <v>-0.5503424461088073</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.545059163445629</v>
+        <v>-1.531503117094026</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3135706502436761</v>
+        <v>-0.3240002859418283</v>
       </c>
     </row>
     <row r="20">
@@ -4580,49 +4580,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6508280176445211</v>
+        <v>0.7210544128154055</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8374410330509292</v>
+        <v>-0.7669789708888146</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4924823660346931</v>
+        <v>-0.4228340994862307</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.007684453379219747</v>
+        <v>0.07684917218094967</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8256134232638956</v>
+        <v>0.8932394220409279</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3565993862460886</v>
+        <v>-0.2872190606392593</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.674378726206413</v>
+        <v>-1.603456513501484</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.264866687256713</v>
+        <v>-2.193677866647832</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.7229072639445704</v>
+        <v>-0.6536748014957325</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.079814199897278</v>
+        <v>-1.010982760387172</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.1748264637956254</v>
+        <v>-0.1073095344109092</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1404433064501944</v>
+        <v>-0.1960840914151945</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.930611604201502</v>
+        <v>-0.9856930728074147</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4342811473876083</v>
+        <v>-0.3904992945020709</v>
       </c>
     </row>
     <row r="21">
@@ -4632,49 +4632,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.8744373274584163</v>
+        <v>0.886959617134039</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5298823994954773</v>
+        <v>-0.5169725899194262</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1115183239597499</v>
+        <v>0.124525455377352</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.070787000608696</v>
+        <v>1.083766143007161</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.879516044603889</v>
+        <v>1.892626848978828</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6225538372418242</v>
+        <v>0.6355967335361896</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.08394153806153781</v>
+        <v>-0.07087528376106178</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5511249368430384</v>
+        <v>-0.5379439275478006</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7350254360420152</v>
+        <v>0.7482241749967784</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4030349660399963</v>
+        <v>0.4164400936928274</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.545431900789772</v>
+        <v>1.55888919449999</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.579815058135203</v>
+        <v>1.593267346855313</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.641425732164393</v>
+        <v>0.6549817785159959</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.365530570127262</v>
+        <v>1.398852143768437</v>
       </c>
     </row>
     <row r="22">
@@ -4684,101 +4684,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.0580388507837597</v>
+        <v>0.02355624137978651</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.8373306440068191</v>
+        <v>-0.824420834430768</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3780168404876676</v>
+        <v>-0.4134625862404206</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6482936397900829</v>
+        <v>0.6612727821885471</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.325135134266752</v>
+        <v>1.287857781064176</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1470233770600657</v>
+        <v>0.110956291146735</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1172435538567385</v>
+        <v>-0.1041772995562624</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5844269526382391</v>
+        <v>-0.5712459433430013</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.6113056566911297</v>
+        <v>0.6245043956458929</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.2388195283367978</v>
+        <v>-0.2254144006839667</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.72339303603502</v>
+        <v>0.7368503297452378</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8089907444425677</v>
+        <v>0.7712284821005611</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.00959749070808158</v>
+        <v>-0.04694411844362634</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5611451523323723</v>
+        <v>0.5894064360858806</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.2074</t>
+          <t>X &lt; -0.2073</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.239809595993016</v>
+        <v>-0.2671755725190863</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.05302416559013778</v>
+        <v>-0.08140693643240127</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1770038226323365</v>
+        <v>-0.2055279426039789</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.6074015893144704</v>
+        <v>0.5783172052427972</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5708784808296414</v>
+        <v>0.5415092490613489</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2973686756028755</v>
+        <v>0.2683364949162979</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1289552370185092</v>
+        <v>-0.1577343701910223</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.05891683994429542</v>
+        <v>-0.04573583064905762</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6475429822387113</v>
+        <v>0.6607417211934745</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2025822027892161</v>
+        <v>-0.189177075136385</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.7108450157265409</v>
+        <v>0.6805653583148654</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4815765568627697</v>
+        <v>0.4514607997337095</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2588031733760303</v>
+        <v>0.2286058938836106</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3213983139071956</v>
+        <v>0.3442487161080194</v>
       </c>
     </row>
     <row r="24">
@@ -4788,49 +4788,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6365848428298264</v>
+        <v>-0.6590536823562161</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.8617686899309902</v>
+        <v>-0.884809753577926</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.814958395010855</v>
+        <v>-0.8382248597045745</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1747695910604747</v>
+        <v>-0.1984333546228711</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3379742469477449</v>
+        <v>-0.3617850085236043</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4778154566065567</v>
+        <v>-0.501423062226813</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8648320272158472</v>
+        <v>-0.8882363071122299</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6408683150071894</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2337070861449178</v>
+        <v>-0.2578148714103676</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8426707109142697</v>
+        <v>-0.8667611557399724</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.126124933762874</v>
+        <v>-0.1508145676085988</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3936790027015675</v>
+        <v>-0.4181943143458753</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9801348797213052</v>
+        <v>-1.004459199947931</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.964961136770647</v>
+        <v>-0.9450637413460328</v>
       </c>
     </row>
     <row r="25">
@@ -4840,49 +4840,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.467956654579154</v>
+        <v>-1.518780710857136</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.679638798845879</v>
+        <v>-1.731853676393207</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.792973359123657</v>
+        <v>-1.845481339304122</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.007236473539407</v>
+        <v>-1.060628464267346</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.7647465415501316</v>
+        <v>-0.8190200584952763</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9323025451183327</v>
+        <v>-0.9861068521108933</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.420231331486434</v>
+        <v>-1.473551506058612</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.229939630910692</v>
+        <v>-1.284006232924263</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8824869347883961</v>
+        <v>-0.9370873684499301</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.44864897178384</v>
+        <v>-1.503439849124767</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.8687712767142983</v>
+        <v>-0.9245327600426663</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9248702025857725</v>
+        <v>-0.9805668500358777</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.373102804178032</v>
+        <v>-1.428703944750168</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.276707805895782</v>
+        <v>-1.230989562509492</v>
       </c>
     </row>
     <row r="26">
@@ -4892,49 +4892,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.051945951640157</v>
+        <v>-1.068486652003273</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.390079806477395</v>
+        <v>-1.406969280183816</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.528743118548412</v>
+        <v>-1.545697037764981</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.632368164014963</v>
+        <v>-0.6498006001921368</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5171138780428493</v>
+        <v>-0.5348020175208106</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8691101858803734</v>
+        <v>-0.8865157295852342</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.433854398558985</v>
+        <v>-1.450981730484834</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.416780427247843</v>
+        <v>-1.434084808464981</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.276902548822925</v>
+        <v>-1.294320507506036</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.925921699056566</v>
+        <v>-1.943264854920336</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.531386946470953</v>
+        <v>-1.549035911482115</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.920924713272477</v>
+        <v>-1.938355366238262</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.424091621072542</v>
+        <v>-2.441388920641664</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.371272235192258</v>
+        <v>-2.355545513566696</v>
       </c>
     </row>
     <row r="27">
@@ -4944,101 +4944,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.222031989125384</v>
+        <v>-1.236102752526058</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9378260557079798</v>
+        <v>-0.9525068978586901</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7336468735370616</v>
+        <v>-0.7485557513438721</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.003723141258959117</v>
+        <v>-0.01898602710252106</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2141561659600342</v>
+        <v>0.1986171756945367</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2921884702638522</v>
+        <v>-0.3073922813611887</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.233601824020113</v>
+        <v>-1.248351250613389</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.516690567240275</v>
+        <v>-1.531435551351258</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.497624881075879</v>
+        <v>-1.512408381134485</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.059050431637857</v>
+        <v>-2.073792567424391</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.818308399387803</v>
+        <v>-1.833245315217063</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.277422061511729</v>
+        <v>-2.292121362294615</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.617276360666942</v>
+        <v>-2.631928559299183</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.652796931531185</v>
+        <v>-2.639081269832936</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.121</t>
+          <t>X &lt; -0.1209</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.441813081204238</v>
+        <v>-1.45368239460506</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.546427523800723</v>
+        <v>-1.558641320538911</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.389832792880867</v>
+        <v>-1.40222501480946</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5639788714524556</v>
+        <v>-0.5767440585447616</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5019184540362573</v>
+        <v>-0.5148517522310598</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5617328027277892</v>
+        <v>-0.5745753824783364</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.627267635061521</v>
+        <v>-1.639629302594656</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.068998720717495</v>
+        <v>-2.081270024547784</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.008552577542865</v>
+        <v>-2.020876606554147</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.593092082681579</v>
+        <v>-2.605349410349824</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.051697204843009</v>
+        <v>-2.064272894853993</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.856224809106777</v>
+        <v>-2.868415072898507</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.010427595854736</v>
+        <v>-3.022654272306518</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.734898737770919</v>
+        <v>-2.723058976199681</v>
       </c>
     </row>
     <row r="29">
@@ -5048,205 +5048,205 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.8974610574202941</v>
+        <v>-0.9074894571077792</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.217872825562687</v>
+        <v>-1.228088131468759</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.9769047097926986</v>
+        <v>-0.9873109536725551</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6043035141685706</v>
+        <v>-0.6148540540427589</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.286936151057219</v>
+        <v>-0.2977400194367306</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6228767231701369</v>
+        <v>-0.6334815404374652</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.648431251463307</v>
+        <v>-1.65861079438033</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.873050216363076</v>
+        <v>-1.883231536609365</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.603515010977063</v>
+        <v>-1.613833819730971</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.035018594259697</v>
+        <v>-2.045325020085379</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.645112880203307</v>
+        <v>-1.655638593260377</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.245776608000277</v>
+        <v>-2.256038962464508</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.378559463986605</v>
+        <v>-2.388854785950336</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.017015038356888</v>
+        <v>-2.007399635540331</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; -0.0864</t>
+          <t>X &lt; -0.08639</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.198101532645204</v>
+        <v>-1.206015632127979</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.39368816921889</v>
+        <v>-1.401787257117512</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.20909484001016</v>
+        <v>-1.217336028289417</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.177289119294215</v>
+        <v>-1.185527503177305</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7363920356087448</v>
+        <v>-0.7448980136307028</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.8566131742961929</v>
+        <v>-0.8650289580857446</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.399295755487671</v>
+        <v>-1.407513864105056</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.445497521676728</v>
+        <v>-1.453777569664318</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.28509915660797</v>
+        <v>-1.293458541006579</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.673648971783834</v>
+        <v>-1.681995143611218</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.096329466969763</v>
+        <v>-1.104945002391204</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.520240115537412</v>
+        <v>-1.528686097734955</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.598194454546707</v>
+        <v>-1.606682475166743</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.44660369947588</v>
+        <v>-1.438998873306979</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.06912</t>
+          <t>X &lt; -0.06911</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.263177578381104</v>
+        <v>-1.269462286040955</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.239471889088996</v>
+        <v>-1.245976526829914</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.9533903788373479</v>
+        <v>-0.9600549925560173</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.097568683633909</v>
+        <v>-1.104167659141929</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6969416975940774</v>
+        <v>-0.7037614472723206</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.152181471789881</v>
+        <v>-1.158799636662387</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.548487354938963</v>
+        <v>-1.554974762576251</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.70155188290056</v>
+        <v>-1.708047344719667</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.632363565761437</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.836360836190622</v>
+        <v>-1.842932610245185</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.578807751317051</v>
+        <v>-1.585505061344776</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.892986690378407</v>
+        <v>-1.899567955822832</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.961212148815605</v>
+        <v>-1.967826847892063</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.728205553955966</v>
+        <v>-1.72192045223747</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.05184</t>
+          <t>X &lt; -0.05183</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.326715290111906</v>
+        <v>-1.33149074317803</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.330992988654614</v>
+        <v>-1.335930327859252</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.30191109662362</v>
+        <v>-1.306900571952674</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.221353979742879</v>
+        <v>-1.226360716710715</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.098363656200952</v>
+        <v>-1.103468723547763</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.426324941701402</v>
+        <v>-1.431292300010092</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.831904378444094</v>
+        <v>-1.836745792207083</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.908286612438012</v>
+        <v>-1.913151769624697</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.781679093639596</v>
+        <v>-1.786596234241827</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.799564846953452</v>
+        <v>-1.804563952642368</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.476909252328085</v>
+        <v>-1.482041338890518</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.967033395375132</v>
+        <v>-1.971998814745753</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.995343359208526</v>
+        <v>-2.000344315705021</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.727052417424602</v>
+        <v>-1.722095805244997</v>
       </c>
     </row>
     <row r="33">
@@ -5256,49 +5256,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.026521965653174</v>
+        <v>-1.030057996212975</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.185873625337834</v>
+        <v>-1.189480400751741</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.314371582931344</v>
+        <v>-1.317969355996055</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.354944595573194</v>
+        <v>-1.358522193621823</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.189298722235485</v>
+        <v>-1.192969782902729</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.469000032409795</v>
+        <v>-1.472563888225466</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.756003416113558</v>
+        <v>-1.759485876125588</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.674879233698412</v>
+        <v>-1.678423566700516</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.562697754215236</v>
+        <v>-1.566283759092983</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.644853979608563</v>
+        <v>-1.648479138248661</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.394244500234166</v>
+        <v>-1.397965346679158</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.843768590682075</v>
+        <v>-1.847348315283213</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.871040666994119</v>
+        <v>-1.874645044407856</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.948867679098058</v>
+        <v>-1.945032178436037</v>
       </c>
     </row>
     <row r="34">
@@ -5308,49 +5308,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.4155539842611233</v>
+        <v>-0.4181618178673006</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.7038491424765567</v>
+        <v>-0.7064584153738309</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.9377986391892534</v>
+        <v>-0.9403618804462397</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.8792261110027653</v>
+        <v>-0.8818010254220212</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.8492765371903914</v>
+        <v>-0.8518896339745794</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.9435520697351976</v>
+        <v>-0.9461236787404559</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.041774271806673</v>
+        <v>-1.0443231415545</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.202127860969647</v>
+        <v>-1.204655846154644</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.18915151760357</v>
+        <v>-1.191687889967724</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.324231722366584</v>
+        <v>-1.326774575269951</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.9592533599312034</v>
+        <v>-0.9619146993609036</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.4043689929834</v>
+        <v>-1.406900280522613</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.342022364457371</v>
+        <v>-1.3445952543697</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.36787797168364</v>
+        <v>-1.365197859480297</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3732</v>
+        <v>3733</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1836919917720508</v>
+        <v>-0.1851338628888612</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3656956938579938</v>
+        <v>-0.3671355014352997</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4790417404921641</v>
+        <v>-0.4804632519429646</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.467970639178283</v>
+        <v>-0.4693921531698777</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4306362656730798</v>
+        <v>-0.4320838291379374</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4929597256963021</v>
+        <v>-0.4943829205697625</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4027488997594872</v>
+        <v>-0.4041993811814777</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6146373302151247</v>
+        <v>-0.6160452181037286</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4202056171011108</v>
+        <v>-0.4216680119531091</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.6935633186789119</v>
+        <v>-0.6949775877756466</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3747878382700875</v>
+        <v>-0.3762940387937732</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.6200234237050992</v>
+        <v>-0.6214637710532784</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.5431915102152232</v>
+        <v>-0.5446652127226059</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.6267710669422897</v>
+        <v>-0.6253570866078846</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_90.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_90.xlsx
@@ -568,1093 +568,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.4924</t>
+          <t>X ≈ -0.492</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.64987030338444</v>
+        <v>16.99981264896572</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.079888434842836</v>
+        <v>-6.248504498212398</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.474747146054561</v>
+        <v>-6.642873491489624</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.722441008868387</v>
+        <v>2.159222178335398</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4.186427361678192</v>
+        <v>1.671488476018148</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.020685857048584</v>
+        <v>6.283369635697952</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.40086292416462</v>
+        <v>1.884130408922871</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.47410629237163</v>
+        <v>5.760660287811852</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.415478448523658</v>
+        <v>5.725326554515881</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>16.65022648334595</v>
+        <v>17.93409713098958</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>20.99195605671297</v>
+        <v>22.07922638044315</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>16.48845210856744</v>
+        <v>17.79728219852908</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.52822284642252</v>
+        <v>13.05993376524193</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.75683612869749</v>
+        <v>13.31223409774825</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.4752</t>
+          <t>X ≈ -0.4748</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.567713359318304</v>
+        <v>0.1207748175796652</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.03793742144619472</v>
+        <v>3.789990876446545</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.126969780426997</v>
+        <v>-1.850425441777354</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.48163252788074</v>
+        <v>11.40351202192412</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.250552719382462</v>
+        <v>5.666918244493289</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.851958250882248</v>
+        <v>3.314349757701429</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.627193265149856</v>
+        <v>-1.999211659625402</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.79245679663461</v>
+        <v>-5.09258395918647</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.854152603715207</v>
+        <v>0.1258840532635759</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.095558504439424</v>
+        <v>4.560610005497601</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.29392916160701</v>
+        <v>9.617022723759689</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.629901928025852</v>
+        <v>7.047429729752864</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.212066483894674</v>
+        <v>6.654179766399736</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.737180109039407</v>
+        <v>4.273332495917593</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.4578</t>
+          <t>X ≈ -0.4575</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.957392791567706</v>
+        <v>8.437183561505037</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.99039996384856</v>
+        <v>9.292794526142835</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.59946712726971</v>
+        <v>11.33471854844441</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.092578902004739</v>
+        <v>6.601329691788955</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10.19753606179427</v>
+        <v>13.41521538377544</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15.13866315512368</v>
+        <v>18.55906439184135</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.41525838122787</v>
+        <v>13.63401736625404</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.985425963112903</v>
+        <v>5.86638626087457</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>14.53848655882071</v>
+        <v>13.13878988323169</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.36972404241409</v>
+        <v>12.31895535701311</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>13.49193674642584</v>
+        <v>14.55532361703742</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.85427019772489</v>
+        <v>17.05508301941864</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>17.76331774126459</v>
+        <v>19.10282817850074</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>15.66804120269014</v>
+        <v>16.91774841376098</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.4406</t>
+          <t>X ≈ -0.4403</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>39</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-8.861990819777169</v>
+        <v>-8.891163039142704</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-10.47023847821293</v>
+        <v>-10.47151114234688</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-15.9802806527187</v>
+        <v>-15.98055989243511</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-13.2970790517522</v>
+        <v>-13.29766689800937</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-16.39580050821849</v>
+        <v>-16.34747971028808</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-21.22086786730577</v>
+        <v>-21.19708447890127</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-16.19170376687072</v>
+        <v>-16.14386608670607</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-26.90269568819237</v>
+        <v>-26.85364650410555</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-21.84895628455558</v>
+        <v>-21.77587894274216</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-27.82670544300109</v>
+        <v>-27.72754712691437</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-28.0383735458155</v>
+        <v>-27.93860807257595</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-33.13665910957951</v>
+        <v>-33.01307844919337</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-33.56518384677565</v>
+        <v>-33.41655954766822</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-25.65575128389198</v>
+        <v>-25.48375252432649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.4234</t>
+          <t>X ≈ -0.4229</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>42</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.645819953851081</v>
+        <v>4.616777734520632</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.8263650611649</v>
+        <v>-8.827626728556105</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.648405668868577</v>
+        <v>2.64827431322054</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-6.720152863838301</v>
+        <v>-6.720695528613376</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-14.38508440625466</v>
+        <v>-14.33675708902992</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-21.21995127604938</v>
+        <v>-21.19617417912669</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-9.426915276370138</v>
+        <v>-9.379047570897825</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-9.895534076468309</v>
+        <v>-9.846415173298851</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5.203460279554186</v>
+        <v>-5.130326084595566</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.054006652648646</v>
+        <v>-5.954788791546108</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.260132979588221</v>
+        <v>-6.160322848731766</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.847588587793794</v>
+        <v>-3.723967491183934</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-13.78995301992238</v>
+        <v>-13.64131579241564</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-13.56783919597882</v>
+        <v>-13.39584043641216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.4061</t>
+          <t>X ≈ -0.4057</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>35</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-18.13349504218277</v>
+        <v>-18.16275868327582</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-25.43985403236307</v>
+        <v>-25.4412706631567</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-22.99159750870542</v>
+        <v>-22.99194282689893</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-20.0180355995835</v>
+        <v>-20.01868158873004</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-17.70983636683081</v>
+        <v>-17.66153825083951</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-25.97092510759968</v>
+        <v>-25.94718323238316</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-26.06249765059695</v>
+        <v>-26.01472267251274</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-35.09340836150891</v>
+        <v>-35.04440830680365</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-26.60365230793876</v>
+        <v>-26.53060264329582</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-24.60572365591878</v>
+        <v>-24.50656541521455</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-19.10700633400586</v>
+        <v>-19.00722788951086</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-13.36633253209725</v>
+        <v>-13.24272762085077</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.64626843023763</v>
+        <v>-16.49763465723667</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-16.42498205312405</v>
+        <v>-16.25298329355479</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.3887</t>
+          <t>X ≈ -0.3885</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6.95450888198247</v>
+        <v>7.988669791853887</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.35124875651028</v>
+        <v>3.790358579184712</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.125779544478782</v>
+        <v>-1.84946477000976</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.996749326113431</v>
+        <v>-1.720433076829721</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.23076927640021</v>
+        <v>-7.459566046997523</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.935365303130475</v>
+        <v>-7.189013384742587</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.021739260714646</v>
+        <v>-7.251709183263969</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.791040730746694</v>
+        <v>-2.46371161025214</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-6.552476553386704</v>
+        <v>-5.129794733795976</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-7.403487755912657</v>
+        <v>-5.954362881493473</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.9095746056176</v>
+        <v>-3.530557791304467</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-7.577776241498484</v>
+        <v>-6.103530077479768</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-21.50975167705382</v>
+        <v>-19.65460496672856</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-23.99254962069032</v>
+        <v>-22.04245697776781</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.3715</t>
+          <t>X ≈ -0.3711</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>49</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>10.74648499124407</v>
+        <v>8.683764964398925</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3.041756504504171</v>
+        <v>3.040642043075373</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.78788637883697</v>
+        <v>10.78778027785097</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.814676449322384</v>
+        <v>2.778847697361776</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.350808672109089</v>
+        <v>8.399309689273643</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>10.68651310623521</v>
+        <v>10.71050079216738</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8.56761514644441</v>
+        <v>8.615592907371784</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>14.21634693665609</v>
+        <v>12.22801978447743</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.0827490855994</v>
+        <v>8.117842275729394</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.236200056991194</v>
+        <v>7.296820884743227</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.994829106009199</v>
+        <v>5.055483731968785</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.9119431276246743</v>
+        <v>-1.004157764101123</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.532429453716951</v>
+        <v>0.6408054772290797</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.799507742795612</v>
+        <v>4.971506502362274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.3542</t>
+          <t>X ≈ -0.3539</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6934197803810562</v>
+        <v>0.215771559388493</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.857791143500265</v>
+        <v>-4.985231062581668</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-6.253453599407358</v>
+        <v>-7.192436768510952</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.563407704810082</v>
+        <v>-1.624893283390428</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.586824760872169</v>
+        <v>8.768900505923114</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>7.885899332185019</v>
+        <v>9.043761208148354</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7.803332118238217</v>
+        <v>8.985503280811912</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>10.9048331915369</v>
+        <v>12.15339551099309</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10.84663226069081</v>
+        <v>12.11949812973395</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.649115746129141</v>
+        <v>5.851061755367191</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.661499711475031</v>
+        <v>3.831884589761252</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.227009037993689</v>
+        <v>-5.194797356781379</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.277382193395837</v>
+        <v>3.497166812671793</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.1106530700802679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.3369</t>
+          <t>X ≈ -0.3367</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>51</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-7.35695230507428</v>
+        <v>-7.386104834714011</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.67102355487355</v>
+        <v>6.669902478487529</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4143941717740631</v>
+        <v>0.4142417110767127</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.41046054463007</v>
+        <v>6.410018086888442</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.918991299383912</v>
+        <v>3.967427445038417</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3042349439993473</v>
+        <v>0.3281305973790936</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-7.60827229672222</v>
+        <v>-7.560414409062169</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.2465416498714958</v>
+        <v>-0.1973915871497525</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3077566833789049</v>
+        <v>-0.2346180971315448</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.94992578282389</v>
+        <v>-10.85074219446859</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-11.1575670837478</v>
+        <v>-11.05778268560339</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.327667274158593</v>
+        <v>-1.20405262748924</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.668601436008984</v>
+        <v>-5.519964790312812</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.483805582533627</v>
+        <v>-3.311806822966965</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.3196</t>
+          <t>X ≈ -0.3194</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.036079460295802</v>
+        <v>0.2663951239260882</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-6.182941365307791</v>
+        <v>-5.462848942227808</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.9621681846828807</v>
+        <v>-0.3187954698012305</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.571692706853888</v>
+        <v>-0.189556566161599</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.03462462229657604</v>
+        <v>-0.6779461808256286</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.073477960579496</v>
+        <v>-0.4055110119705319</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.969570939862543</v>
+        <v>-3.23838474354914</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.843172517936082</v>
+        <v>-5.091020502367471</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.905981047721959</v>
+        <v>-5.12963821537685</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.684601792137144</v>
+        <v>2.370013630410561</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.887693076974536</v>
+        <v>3.554320305100134</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.922922328457915</v>
+        <v>3.613512985043165</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.91172853605427</v>
+        <v>4.60794727470546</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.729947524341391</v>
+        <v>3.469238928665817</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.3024</t>
+          <t>X ≈ -0.3022</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>84</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.21596217711587</v>
+        <v>-6.059040603680309</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.703949138553234</v>
+        <v>-2.891551168466911</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2748166878249521</v>
+        <v>-0.9120717736171429</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7825761957812816</v>
+        <v>-0.7830333662979143</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.429500457179515</v>
+        <v>3.477962551590416</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.103129354774794</v>
+        <v>4.939306245300685</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.0802518362968172</v>
+        <v>-1.059947867184199</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.762897520279225</v>
+        <v>-3.902201003880201</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.307598829711154</v>
+        <v>3.191974160220894</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.081607444974438</v>
+        <v>-0.008291632508495184</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.635026949223239</v>
+        <v>4.545392736713772</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>10.43023108887122</v>
+        <v>9.364065420365343</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.63293903323364</v>
+        <v>6.591448159992311</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>15.00358937544839</v>
+        <v>13.98511194453888</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.2851</t>
+          <t>X ≈ -0.2848</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.471145818408438</v>
+        <v>-1.051981772353201</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9622216381303303</v>
+        <v>0.3172255411949862</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.47163671733464</v>
+        <v>-3.055080358290375</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.78545795937044</v>
+        <v>-1.435302747949798</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.440418509298262</v>
+        <v>-4.906515092949192</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-9.26285056927091</v>
+        <v>-6.79605231844922</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-10.90884698915002</v>
+        <v>-9.836972467715199</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-9.818573171461374</v>
+        <v>-7.325083214276333</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-9.88295804123878</v>
+        <v>-7.364758616257696</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.05284314295308</v>
+        <v>-3.717472248165066</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-7.820491502092267</v>
+        <v>-5.413967163051623</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-9.34997811652719</v>
+        <v>-6.849045974969535</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-9.772711250996437</v>
+        <v>-8.738144497614442</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-7.987482053122399</v>
+        <v>-6.999251950272168</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.2679</t>
+          <t>X ≈ -0.2676</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>99</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>8.093502984765408</v>
+        <v>6.916315983024901</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6.491794223813478</v>
+        <v>7.238485260072899</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>8.113152728037207</v>
+        <v>10.86737386053532</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.216970866823246</v>
+        <v>7.986036658198344</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5.695667840036243</v>
+        <v>8.030465684919264</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.979294961902411</v>
+        <v>6.287813810941877</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>5.912457519153136</v>
+        <v>9.792314744188261</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.439696779783041</v>
+        <v>5.832842015621345</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.3709233984546</v>
+        <v>5.354401692343416</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5051789583613626</v>
+        <v>2.055370608699555</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.309755908417472</v>
+        <v>2.418712249225941</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.354017434694434</v>
+        <v>3.487096170824408</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.944518272422492</v>
+        <v>5.112742598945196</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>1.322774282201259</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.2505</t>
+          <t>X ≈ -0.2504</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.759605826077646</v>
+        <v>2.121884325522139</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8077338680152764</v>
+        <v>0.5155495075503964</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.019045525926977</v>
+        <v>2.118877211254009</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.407429557117354</v>
+        <v>5.277341016752366</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7.175602012576014</v>
+        <v>6.118559522373189</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5.519486700751266</v>
+        <v>5.058861776926925</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8.045802701489137</v>
+        <v>6.995098204379005</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>8.234585784647429</v>
+        <v>8.524325580953331</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.175698221678545</v>
+        <v>7.822760481431914</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>7.982220510555663</v>
+        <v>7.659859631560437</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.39186096900677</v>
+        <v>10.12050247458292</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>11.08273115032303</v>
+        <v>10.55313708916373</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>9.359519418788679</v>
+        <v>8.828618558378885</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10.89527938478574</v>
+        <v>9.747016706443908</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.2333</t>
+          <t>X ≈ -0.233</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.62178981713884</v>
+        <v>-5.202706981656654</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.871193475739751</v>
+        <v>-3.155765386482571</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.948497286276933</v>
+        <v>-4.514376022617014</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.084353768496847</v>
+        <v>-3.058629150884165</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.631026380878474</v>
+        <v>-3.549681530798004</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.323747578792478</v>
+        <v>-4.601356323304813</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3245603327612372</v>
+        <v>-2.015295748611109</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.7986261095900176</v>
+        <v>-2.484534627034009</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1773508945071143</v>
+        <v>-1.857874561315349</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.438156850177144</v>
+        <v>-5.997462197791158</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.642866160783889</v>
+        <v>-5.538971769895504</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-4.610161732440297</v>
+        <v>-5.480805032530611</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.655601038641102</v>
+        <v>-6.168833994017099</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.724301781013907</v>
+        <v>-6.584109121370666</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ -0.216</t>
+          <t>X ≈ -0.2158</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.000613075226319</v>
+        <v>-1.742035331308045</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4.319144180367111</v>
+        <v>4.47716753886823</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.023980871376345</v>
+        <v>0.9579060999675377</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.09699906696587846</v>
+        <v>-0.4727905400015473</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.875643316188778</v>
+        <v>-4.088610032712495</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.202541761840557</v>
+        <v>0.8709775519916647</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4771599866105518</v>
+        <v>-0.752701987820025</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.063736040907848</v>
+        <v>2.424332365140927</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8789413976166998</v>
+        <v>0.3055967744297092</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0238003181369919</v>
+        <v>-0.5239897628343329</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3515834628226884</v>
+        <v>-0.2065989429218504</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.443332807482811</v>
+        <v>-2.231765538890407</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.859920594523054</v>
+        <v>1.01454777966017</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.105833116952539</v>
+        <v>-1.565483293556213</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ -0.1987</t>
+          <t>X ≈ -0.1986</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.711697972710127</v>
+        <v>-3.972100128980557</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.12536151891652</v>
+        <v>-7.309663179048556</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.750705107638801</v>
+        <v>-5.949015202451235</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.206475807420475</v>
+        <v>-5.819131161236434</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-7.346650462112166</v>
+        <v>-7.477970945463206</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.454382604500559</v>
+        <v>-6.620390105006848</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.542906385740899</v>
+        <v>-6.681046194232309</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.241182803823882</v>
+        <v>-5.392492989703371</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7.340672108719055</v>
+        <v>-7.768646885389877</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6.097027334598046</v>
+        <v>-6.838089501292579</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.560802990556745</v>
+        <v>-7.627025270466099</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.118140814532921</v>
+        <v>-8.153653854738629</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-10.49687154950327</v>
+        <v>-11.47278838948959</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-10.86285187560796</v>
+        <v>-11.80853884911151</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.1815</t>
+          <t>X ≈ -0.1813</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>129</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-11.39564471270489</v>
+        <v>-11.42484050705752</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-11.4564432088695</v>
+        <v>-11.45762999531416</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-13.40160219052376</v>
+        <v>-13.40175558052808</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-10.94579565158639</v>
+        <v>-10.94629014396439</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-6.057728615534977</v>
+        <v>-6.009182695769205</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-6.535548384349497</v>
+        <v>-6.511590975399884</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-8.170646340514715</v>
+        <v>-8.122634661524394</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-8.637714984301631</v>
+        <v>-8.588467421907914</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-8.698697140824407</v>
+        <v>-8.625440031044711</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-8.773422138704831</v>
+        <v>-8.674074813410257</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-9.753317095414637</v>
+        <v>-9.653409059395962</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-7.393357547710302</v>
+        <v>-7.269660926682057</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-6.263120804124483</v>
+        <v>-6.114431256346656</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-4.486997556998723</v>
+        <v>-4.314998797432061</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ -0.1642</t>
+          <t>X ≈ -0.164</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.493926736761388</v>
+        <v>3.114888175112874</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.882740643697559</v>
+        <v>2.156711089957305</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.487969258942378</v>
+        <v>1.762973101642316</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.504986855360926</v>
+        <v>3.767857142856997</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.337766484655027</v>
+        <v>2.653608001905212</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.1194172438500019</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.223154750636432</v>
+        <v>-0.8842625685014625</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.948085029643153</v>
+        <v>-2.600095328884656</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.895859638996114</v>
+        <v>-4.512067938021453</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-6.374709252935894</v>
+        <v>-5.960896518836293</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.837272046416501</v>
+        <v>-7.415036966372526</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-11.57647879972141</v>
+        <v>-11.10687022900763</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-12.62556047064488</v>
+        <v>-12.1270281555716</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-13.65768645563848</v>
+        <v>-13.12798329355609</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ -0.1468</t>
+          <t>X ≈ -0.1467</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>158</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.113827422939558</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.135745977667639</v>
+        <v>3.50164779881792</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.171354339748049</v>
+        <v>7.5382895573388</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.035756698526143</v>
+        <v>6.40235081374307</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>8.396201322645922</v>
+        <v>7.811835850006631</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.161929782660756</v>
+        <v>5.552975799205299</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.013928284153934</v>
+        <v>0.4290285707393409</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.61769732165812</v>
+        <v>-3.201361151669467</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.944502262990881</v>
+        <v>-4.504156545616389</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.528598274510756</v>
+        <v>-4.062162341621246</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.999122217580933</v>
+        <v>-5.532125573967463</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.739781621412547</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.751983526134239</v>
+        <v>-5.236205370761191</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.792070660717833</v>
+        <v>-6.252983293556234</v>
       </c>
     </row>
     <row r="27">
@@ -1667,368 +1667,368 @@
         <v>165</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.996067545685868</v>
+        <v>-4.631323946098831</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.63755666905287</v>
+        <v>-8.638743455497654</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-9.032328053807767</v>
+        <v>-8.426420837751614</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.083921092037585</v>
+        <v>-6.478354978354709</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-8.834331857254625</v>
+        <v>-8.179725331428251</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.688472979134694</v>
+        <v>-3.058454964124337</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.197425762643149</v>
+        <v>-5.543353477592362</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-8.482676224611708</v>
+        <v>-7.827368056157525</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7.937597775074018</v>
+        <v>-7.258280059233577</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-8.7875165714036</v>
+        <v>-8.08210864004856</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.749793487239685</v>
+        <v>-4.043824845160266</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-9.563900183369348</v>
+        <v>-8.834142956280502</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-7.559808612440058</v>
+        <v>-6.805058458601764</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.69770932584975</v>
+        <v>-2.919649960222756</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.1123</t>
+          <t>X ≈ -0.1122</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.954981405363078</v>
+        <v>5.221846937999494</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.318154286658171</v>
+        <v>2.607742017792269</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.461844440364736</v>
+        <v>3.244931864529171</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.023315031431473</v>
+        <v>-1.264359351988276</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.028139005216488</v>
+        <v>1.854638929740268</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.26423055489213</v>
+        <v>-1.480822974121338</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.861761426978809</v>
+        <v>-2.056942980872442</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2352724933370141</v>
+        <v>0.05454384637319265</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.738392900916807</v>
+        <v>2.594890824865139</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.939756155868878</v>
+        <v>3.832917914153256</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.709413971967884</v>
+        <v>2.597849631565623</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.282253662784754</v>
+        <v>4.20240812150783</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.374923322291743</v>
+        <v>4.322714112469775</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.626299998159176</v>
+        <v>5.602686809536806</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ -0.09504</t>
+          <t>X ≈ -0.09496</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>222</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.282717832336154</v>
+        <v>-4.311913626688785</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.191201222697231</v>
+        <v>-3.192388009141887</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.585972607452319</v>
+        <v>-3.586125997456641</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-7.05935106746761</v>
+        <v>-7.059845559845613</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-5.345388368311006</v>
+        <v>-5.296842448545235</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.246212536874118</v>
+        <v>-3.222255127924505</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1.173581608364273</v>
+        <v>1.221593287354594</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.958765216829732</v>
+        <v>3.008012779223449</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.996882159406063</v>
+        <v>2.070139269185759</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.047864263977097</v>
+        <v>2.14721158927167</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.545865808419556</v>
+        <v>4.645773844438231</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.931595312126241</v>
+        <v>6.055291933154486</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.412345359713775</v>
+        <v>6.561034907491603</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.38582875768811</v>
+        <v>4.557827517254772</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.07775</t>
+          <t>X ≈ -0.07769</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>214</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.013626310908187</v>
+        <v>-2.042822105260818</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.5807950726634488</v>
+        <v>0.579608286218793</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.055182566413194</v>
+        <v>2.055029176408873</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1510408881293515</v>
+        <v>-0.1515353805073545</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2220407215988729</v>
+        <v>-0.1734948018331011</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.280405088613179</v>
+        <v>-3.232393409622858</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.682053171652207</v>
+        <v>-4.63280560925849</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-5.677614767427315</v>
+        <v>-5.604357657647618</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.723795246000172</v>
+        <v>-3.624447920705599</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.19952444164354</v>
+        <v>-7.099616405624865</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.230566850035821</v>
+        <v>-6.106870229007576</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-6.183427983723121</v>
+        <v>-6.034738435945293</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.023112894244299</v>
+        <v>-4.851114134677637</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.06047</t>
+          <t>X ≈ -0.06042</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>234</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.053565603183927</v>
+        <v>-2.082761397536558</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.382700414196421</v>
+        <v>-2.383887200641077</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.341574363054121</v>
+        <v>-5.341727753058443</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.647246655363141</v>
+        <v>-2.647741147741144</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.749638772561411</v>
+        <v>-5.701092852795639</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-5.10962467484206</v>
+        <v>-5.061612995851739</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.294642036577521</v>
+        <v>-4.245394474183804</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.500923338399431</v>
+        <v>-3.427666228619735</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.359389143276303</v>
+        <v>-1.26004181798173</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2820390194852607</v>
+        <v>-0.1821309834665854</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.811763431232457</v>
+        <v>-2.688066810204212</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.377213429845014</v>
+        <v>-2.228523882067186</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.724127352268049</v>
+        <v>-1.552128592701386</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ -0.04319</t>
+          <t>X ≈ -0.04316</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>247</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.579812714404916</v>
+        <v>2.550616920052285</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.5637683217459539</v>
+        <v>0.5625815353012982</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.450436261389655</v>
+        <v>-1.450589651393976</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-2.93964431618182</v>
+        <v>-2.940138808559823</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-2.263358970492092</v>
+        <v>-2.21481305072632</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.965984940857005</v>
+        <v>-1.942027531907392</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8361204013377872</v>
+        <v>-0.7881087223474665</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.125960752446325</v>
+        <v>1.175208314840042</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.064978595923549</v>
+        <v>1.138235705703245</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2150597995936891</v>
+        <v>0.3144071248882625</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3944996582616938</v>
+        <v>-0.2945916222430185</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3601215059063207</v>
+        <v>-0.2364248848780761</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.375414059624589</v>
+        <v>-0.2267245118467613</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.603119704944568</v>
+        <v>-4.431120945377906</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ -0.02592</t>
+          <t>X ≈ -0.0259</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.856636712081652</v>
+        <v>7.573921788558373</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.823509690747812</v>
+        <v>5.570576636175652</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.162915521182647</v>
+        <v>3.916334446180279</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.558963449581093</v>
+        <v>5.306722689075578</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.754851111675265</v>
+        <v>3.556969346442983</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.161929782660565</v>
+        <v>5.930595201396365</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.608864993014699</v>
+        <v>8.390947515532297</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.188209851337653</v>
+        <v>4.983938284560743</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.861404910004758</v>
+        <v>3.686461473743236</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.011486113674898</v>
+        <v>2.862632892928275</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.916489596764933</v>
+        <v>4.75933278152668</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.528926820850224</v>
+        <v>4.817499518891502</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.796539680616959</v>
+        <v>6.103013861235262</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.444216259113489</v>
+        <v>6.772226790477475</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ -0.00864</t>
+          <t>X ≈ -0.00863</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="inlineStr"/>
@@ -2182,1509 +2182,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.5011</t>
+          <t>X &gt; -0.5007</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4007</v>
+        <v>4018</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.006646158520375423</v>
+        <v>0.007873786623804335</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02392596037350359</v>
+        <v>-0.02381000185425108</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.08169680352494879</v>
+        <v>-0.08146720612622005</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.01228367407009046</v>
+        <v>0.01227124414809566</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.03936022861752519</v>
+        <v>-0.04132619228399648</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.002296142272783186</v>
+        <v>-0.00331338439259099</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02357967848316633</v>
+        <v>-0.02556691632739927</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.103242716845287</v>
+        <v>-0.1050655078110978</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0009531634541914968</v>
+        <v>-0.004082603693838394</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08916431284205117</v>
+        <v>-0.09316902007959982</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.03053103730391626</v>
+        <v>-0.03472112454213061</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.04281803397510231</v>
+        <v>0.03740837795754004</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.06085914295810113</v>
+        <v>0.0543291472401819</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.07614098156653881</v>
+        <v>0.06856971789238742</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.4838</t>
+          <t>X &gt; -0.4834</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3985</v>
+        <v>3995</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.07971543023420935</v>
+        <v>-0.08995214424825804</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.001534197653725755</v>
+        <v>0.01202678748648367</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05744407892378689</v>
+        <v>-0.04369190085379415</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.01371970393883259</v>
+        <v>-8.917424647592043e-05</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.06268954530171555</v>
+        <v>-0.05118720288998446</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.03950705384492892</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.04800571041748469</v>
+        <v>-0.03656141907602262</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1505957101207684</v>
+        <v>-0.1388356438059191</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.04741777963072735</v>
+        <v>-0.03706793802145114</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.181577511716867</v>
+        <v>-0.1969555335901276</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.146589937195607</v>
+        <v>-0.1620354656221537</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.04797342139278982</v>
+        <v>-0.06483870536489889</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.002448762054754638</v>
+        <v>-0.02054667408998512</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.0116553370905379</v>
+        <v>-0.007676660264479551</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.4665</t>
+          <t>X &gt; -0.4661</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3948</v>
+        <v>3957</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.09515485911298782</v>
+        <v>-0.09197580473585276</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.001193032689094764</v>
+        <v>-0.02425388862685907</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.02867699408193403</v>
+        <v>-0.02634141448658056</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1120804011468763</v>
+        <v>-0.1096006338002908</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1312280366374097</v>
+        <v>-0.106099511962654</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.09806944939836626</v>
+        <v>-0.07171492820397418</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.04257766089239112</v>
+        <v>-0.01771362803712861</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1164647931498948</v>
+        <v>-0.09126363572291751</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01174169338678155</v>
+        <v>-0.03863280425063209</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2404057874508467</v>
+        <v>-0.2426435524138171</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2538085812320006</v>
+        <v>-0.2559460572816192</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1293010272510671</v>
+        <v>-0.1331394889217492</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.07943383401527626</v>
+        <v>-0.08464563914902357</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.04200332971850429</v>
+        <v>-0.04878819626016195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.4492</t>
+          <t>X &gt; -0.4489</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3905</v>
+        <v>3916</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1838256783138306</v>
+        <v>-0.1812749707256174</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1222272193347109</v>
+        <v>-0.1218021483320442</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1457090548292186</v>
+        <v>-0.1452902036796715</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1804031540368882</v>
+        <v>-0.1798631831744473</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2449634671707202</v>
+        <v>-0.2476658834451015</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2658490913943865</v>
+        <v>-0.2667767137304935</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1577343701910223</v>
+        <v>-0.1606454387536687</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1506213366887579</v>
+        <v>-0.1536394390325384</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.1719618764456499</v>
+        <v>-0.1765986699775866</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3682510070882827</v>
+        <v>-0.3741618249588896</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.4051701815109539</v>
+        <v>-0.4110180840045743</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3053045004070114</v>
+        <v>-0.3130978961847646</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2759097156380719</v>
+        <v>-0.2855359421428076</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2149948572200628</v>
+        <v>-0.2264255816051204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.432</t>
+          <t>X &gt; -0.4316</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3866</v>
+        <v>3877</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.09628081527268506</v>
+        <v>-0.09365938272760843</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01783703850277618</v>
+        <v>-0.0176910699811188</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.01402925151266032</v>
+        <v>0.01400190822681679</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.0480828332891079</v>
+        <v>-0.04790694255577677</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.0820346920541013</v>
+        <v>-0.08571263628315506</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.05445598941287244</v>
+        <v>-0.05623196190133228</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.004015450416964939</v>
+        <v>0.0001349598200093283</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1192521500439412</v>
+        <v>0.1149445887048373</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.04671447686947516</v>
+        <v>0.04067549319956498</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.09125159606900013</v>
+        <v>-0.0990052536985786</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1264079127039466</v>
+        <v>-0.1341091313209759</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.02589643848531864</v>
+        <v>0.01584181017771868</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.05991069075466982</v>
+        <v>0.04773976603761554</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.04165012483896646</v>
+        <v>0.02764605903612249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.4147</t>
+          <t>X &gt; -0.4143</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3824</v>
+        <v>3835</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1483645580297903</v>
+        <v>-0.1452469600221136</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.07890934668336058</v>
+        <v>0.07879323188593901</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.01490479909637088</v>
+        <v>-0.01484801120205503</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.0251982706028997</v>
+        <v>0.02517183726545369</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.07505947321693185</v>
+        <v>0.07036138379907442</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1780102245093929</v>
+        <v>0.1752876138805348</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.107597848566833</v>
+        <v>0.1028535168708942</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2292471870506105</v>
+        <v>0.2240390111309623</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.104378530156545</v>
+        <v>0.09730706197854744</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.02576108551032519</v>
+        <v>-0.03487411716933764</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.0590395934546919</v>
+        <v>-0.06811148435063785</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.06843994557311106</v>
+        <v>0.0567993044820696</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.212027394689926</v>
+        <v>0.1976590185682667</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1911267334881188</v>
+        <v>0.1746568628976277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.3974</t>
+          <t>X &gt; -0.3971</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3789</v>
+        <v>3800</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.01776887214845146</v>
+        <v>0.02070380584996201</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3146329461203123</v>
+        <v>0.3138464519718553</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1973370179625675</v>
+        <v>0.1967831252583139</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.210342948738699</v>
+        <v>0.2097862767154055</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.2393432827713511</v>
+        <v>0.2336815120128577</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4195548897571584</v>
+        <v>0.4158893190434796</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3493379759014132</v>
+        <v>0.3434101396678528</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5555319440312445</v>
+        <v>0.548879973269834</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3510877091835596</v>
+        <v>0.3425641250534497</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2012905613527707</v>
+        <v>0.1905230395231783</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1169115376931842</v>
+        <v>0.1063277456968876</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1925405094998638</v>
+        <v>0.1792949472154035</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3677519536428022</v>
+        <v>0.3514314603190982</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3446141464021863</v>
+        <v>0.3259640748649559</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.3801</t>
+          <t>X &gt; -0.3798</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3752</v>
+        <v>3762</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.05063714607219794</v>
+        <v>-0.05978069905917494</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2649648264549569</v>
+        <v>0.2787301678585976</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2301076237222475</v>
+        <v>0.2174522959175746</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2419693917476309</v>
+        <v>0.2292834419027372</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.303147697667228</v>
+        <v>0.3113910833159892</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4822233458170899</v>
+        <v>0.4927065180716284</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4121657631494955</v>
+        <v>0.4201285166671624</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5983952673166257</v>
+        <v>0.5793101912852023</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4191665678496364</v>
+        <v>0.3978404771630366</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2762843773812449</v>
+        <v>0.2525925942809266</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.166479764586164</v>
+        <v>0.1430639632423549</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2691667674388114</v>
+        <v>0.2427578262527277</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5834949265467984</v>
+        <v>0.5535126363498861</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5846128296064563</v>
+        <v>0.5519077218612409</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.3628</t>
+          <t>X &gt; -0.3625</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3703</v>
+        <v>3713</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1935102178325252</v>
+        <v>-0.1751681855955169</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2282208912066679</v>
+        <v>0.242281559755817</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.09040166666024163</v>
+        <v>0.07795698993461997</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1814609807778282</v>
+        <v>0.1956371589731702</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1966569097256539</v>
+        <v>0.2046558256558981</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3471949368890606</v>
+        <v>0.357863555660991</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3042486635595836</v>
+        <v>0.3119739906384709</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4181955287809416</v>
+        <v>0.4255836170685612</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2912930751761991</v>
+        <v>0.2959605719301379</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1577221661198678</v>
+        <v>0.159630788131544</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.07612353511554204</v>
+        <v>0.07823536947247334</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2606612201395606</v>
+        <v>0.2592132164836229</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5577056227846171</v>
+        <v>0.5523606435669421</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5288391729101889</v>
+        <v>0.4935828254851131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.3456</t>
+          <t>X &gt; -0.3453</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3647</v>
+        <v>3658</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1858340633212308</v>
+        <v>-0.181046175200251</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3216721316628224</v>
+        <v>0.3208800272868615</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1878121122044618</v>
+        <v>0.1872712755318062</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2236086765258207</v>
+        <v>0.2230098146128583</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.08318024406505486</v>
+        <v>0.07588779465132944</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2314374797635921</v>
+        <v>0.2272664067034142</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1890995893994472</v>
+        <v>0.1815628066692199</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2571723017136804</v>
+        <v>0.2492496492812819</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1292149302930525</v>
+        <v>0.1181873172337973</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.08875642976655485</v>
+        <v>0.07405705844374211</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.03642486062249617</v>
+        <v>0.02179723193395233</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3602799573085989</v>
+        <v>0.3412172026863587</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5312998405103642</v>
+        <v>0.508083896901887</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5259365100798803</v>
+        <v>0.4993403805827796</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.3283</t>
+          <t>X &gt; -0.328</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3596</v>
+        <v>3607</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08413021728969028</v>
+        <v>-0.07917259836764856</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2316229318341883</v>
+        <v>0.231110095207228</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1845986291571791</v>
+        <v>0.1840621010896655</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1358641144364654</v>
+        <v>0.1355306291717611</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.02877914177883412</v>
+        <v>0.02086463907335911</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.230405035192959</v>
+        <v>0.2258402703783702</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2996852307209679</v>
+        <v>0.2910279683000141</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2643161870114596</v>
+        <v>0.255564787362232</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1354122473946262</v>
+        <v>0.1231756943152078</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2453117114245416</v>
+        <v>0.228524694123962</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.195182810890266</v>
+        <v>0.1784533383366167</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3842191421820189</v>
+        <v>0.3630660414273947</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6192294748547766</v>
+        <v>0.593315525138074</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5828043762432031</v>
+        <v>0.5532268533804157</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.311</t>
+          <t>X &gt; -0.3108</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3525</v>
+        <v>3535</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1066933058311292</v>
+        <v>-0.08621103570997946</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3608240850532169</v>
+        <v>0.3470832354322084</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2076966273933891</v>
+        <v>0.1943041789126241</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1270857229296212</v>
+        <v>0.1421519242393643</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.02866140302230491</v>
+        <v>0.03509784389166981</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2566676430510668</v>
+        <v>0.2386994761291774</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3856759223837898</v>
+        <v>0.3629141678058616</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3873322715650147</v>
+        <v>0.36446270556889</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2570970485161297</v>
+        <v>0.2301637003966235</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2163217551889076</v>
+        <v>0.1849073805701735</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1409506892187764</v>
+        <v>0.1096945203431332</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3330849787137709</v>
+        <v>0.2968617472434261</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5529124724873498</v>
+        <v>0.5115465050620216</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5395569539694449</v>
+        <v>0.4938342453406506</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.2937</t>
+          <t>X &gt; -0.2935</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3441</v>
+        <v>3451</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.06685467010259316</v>
+        <v>0.05917223977814245</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.4112283137027219</v>
+        <v>0.4259140931336063</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2060581254822438</v>
+        <v>0.2212342223819093</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1492919423924803</v>
+        <v>0.1646716473356094</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.05435820771562305</v>
+        <v>-0.04870413682311181</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1139466945521477</v>
+        <v>0.1242830841817977</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3931317849909632</v>
+        <v>0.3975477264668754</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.4642341322203194</v>
+        <v>0.4683165889631908</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1582181907362923</v>
+        <v>0.1580709508674332</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1951988264060063</v>
+        <v>0.189609993464579</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.006832001093123097</v>
+        <v>0.001726206760068294</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.08659841281628644</v>
+        <v>0.07615902091996674</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3800783454595447</v>
+        <v>0.3635570124470817</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1864681067145071</v>
+        <v>0.1654461471857189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.2765</t>
+          <t>X &gt; -0.2762</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3377</v>
+        <v>3384</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1149541759553259</v>
+        <v>0.08117203848168231</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4372575695266292</v>
+        <v>0.428066023683229</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2947085459561123</v>
+        <v>0.2861021529094003</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2049105369180495</v>
+        <v>0.1963496273841088</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.06666869761493643</v>
+        <v>0.0474759264335276</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2916532461910819</v>
+        <v>0.2612991811014993</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6073238612554093</v>
+        <v>0.6001815482783996</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6591111436019119</v>
+        <v>0.6226185354221272</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3485158747298982</v>
+        <v>0.3070158625096795</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.313610045250833</v>
+        <v>0.2669665272084316</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.155173340804069</v>
+        <v>0.1089518142592993</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.265437885092858</v>
+        <v>0.2132715311813769</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5724912960586508</v>
+        <v>0.5437620955363727</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3413786220327069</v>
+        <v>0.3073003943871626</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.2592</t>
+          <t>X &gt; -0.259</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3278</v>
+        <v>3285</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1260087075322218</v>
+        <v>-0.124818600942902</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2544024356723327</v>
+        <v>0.2228205124495588</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>-0.03278548759439559</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.08374092963903479</v>
+        <v>-0.038408063955508</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1033346321897355</v>
+        <v>-0.1931073265619361</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1802815165219513</v>
+        <v>0.07967819225699202</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4471017038021259</v>
+        <v>0.323158356072895</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5449323827776524</v>
+        <v>0.4655981017722794</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2572351105905639</v>
+        <v>0.1549028648982542</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.307824406935417</v>
+        <v>0.2130694179032204</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1203033974868859</v>
+        <v>0.03934259567126475</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.202359979232412</v>
+        <v>0.1146083228633756</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.5008528974436359</v>
+        <v>0.4060667926939061</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.3779465618863966</v>
+        <v>0.2766970717407133</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.2419</t>
+          <t>X &gt; -0.2417</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3125</v>
+        <v>3135</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2183283950977639</v>
+        <v>-0.2323163486206496</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2273113287448183</v>
+        <v>0.2088143404351683</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.08636330427158612</v>
+        <v>-0.1357358559603412</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2258668655623097</v>
+        <v>-0.2927501252333897</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4597113703174713</v>
+        <v>-0.4951009556975805</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.08112596929792204</v>
+        <v>-0.1585602567702722</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.07506930295537018</v>
+        <v>0.003926784383608606</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.168446952222105</v>
+        <v>0.08001305492152255</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1304528433282997</v>
+        <v>-0.211980274648802</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.06791402629783505</v>
+        <v>-0.1432363339464047</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.38259206121473</v>
+        <v>-0.4430095516450763</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3303429933041855</v>
+        <v>-0.3848428142801836</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.0671325845585784</v>
+        <v>0.003073885244866403</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1369820531227504</v>
+        <v>-0.1764282696326447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.2246</t>
+          <t>X &gt; -0.2244</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2978</v>
+        <v>2984</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.04839720229647071</v>
+        <v>0.0192014079438394</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.3802596854470437</v>
+        <v>0.3790728990023879</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1042793066601817</v>
+        <v>0.0858374232504957</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1341282575262568</v>
+        <v>-0.1527877482651405</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3525309450144292</v>
+        <v>-0.3405293515286232</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.07893627939102998</v>
+        <v>0.0662595173740641</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.09479581620263389</v>
+        <v>0.1061059407114229</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.2161836010086802</v>
+        <v>0.209787418184014</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1281378622929381</v>
+        <v>-0.1286927286412194</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1478098471441669</v>
+        <v>0.1530063287347474</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1722964626127563</v>
+        <v>-0.1851374688850882</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1190826324401826</v>
+        <v>-0.1269707315201956</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.3002561045754888</v>
+        <v>0.3153922799394309</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.08945716783090774</v>
+        <v>0.1478209959881482</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.2073</t>
+          <t>X &gt; -0.2072</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2790</v>
+        <v>2792</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1864667120363563</v>
+        <v>0.140317974539947</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1148438126710687</v>
+        <v>0.09725550256462157</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.04230658473665017</v>
+        <v>0.02586708445047492</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1497024284956083</v>
+        <v>-0.1307818256242399</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1151312583546513</v>
+        <v>-0.08278168290853216</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.003223795268979757</v>
+        <v>0.01092074135452492</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1333362072165656</v>
+        <v>0.1651643655961053</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.02430551545273829</v>
+        <v>0.05749779432451163</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1959984002366753</v>
+        <v>-0.1585579093681559</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1561660447976863</v>
+        <v>0.1995619338856258</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2075973321403026</v>
+        <v>-0.1836616082063429</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.02985000415773698</v>
+        <v>0.0177716048032508</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1951604328514236</v>
+        <v>0.2673128186405762</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.170000025730296</v>
+        <v>0.2656413482777253</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.1901</t>
+          <t>X &gt; -0.1899</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2621</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4378172773633935</v>
+        <v>0.4086214830107622</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.5816865066956041</v>
+        <v>0.5804997202509483</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4158353813835234</v>
+        <v>0.415681991379202</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2408335123812648</v>
+        <v>0.2403390200032618</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3511513610406283</v>
+        <v>0.3996972808064001</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4196051312327569</v>
+        <v>0.44356254018237</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5638150314095469</v>
+        <v>0.6118267103998676</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.3638200236395974</v>
+        <v>0.4130675860333142</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.2646844905429973</v>
+        <v>0.3379416003226936</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.559366991427936</v>
+        <v>0.6587143167225094</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2020523268724332</v>
+        <v>0.3019603628911085</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.4271973620968978</v>
+        <v>0.5508939831251425</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.884574169981498</v>
+        <v>1.033263717759326</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8813895607650792</v>
+        <v>1.053388320331742</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.1728</t>
+          <t>X &gt; -0.1726</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2492</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.050384129979285</v>
+        <v>1.021188335626654</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.20484811717229</v>
+        <v>1.203661330727634</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.131104019736668</v>
+        <v>1.130950629732347</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.819916643260818</v>
+        <v>0.819422150882815</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.682911199314411</v>
+        <v>0.7314571190801828</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.7796431743748542</v>
+        <v>0.8036005833244673</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.015960102428103</v>
+        <v>1.063971781418424</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.829790335045864</v>
+        <v>0.8790378974395807</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.7286797676081633</v>
+        <v>0.8019368773878597</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.042484887811213</v>
+        <v>1.141832213105786</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7173984968062257</v>
+        <v>0.817306532824901</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.8320334709914121</v>
+        <v>0.9557300920196568</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.254579246891481</v>
+        <v>1.403268794669309</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.159287609798596</v>
+        <v>1.331286369365259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; -0.1555</t>
+          <t>X &gt; -0.1554</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.8838503646649585</v>
+        <v>0.8775382608763138</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.15864798355998</v>
+        <v>1.138271981895407</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.106782728252007</v>
+        <v>1.087587166822566</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.6369221453080058</v>
+        <v>0.6171281548639982</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.570128520202033</v>
+        <v>0.5995771271196304</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8246392836562322</v>
+        <v>0.8294809992833265</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.168561586198891</v>
+        <v>1.197641376610179</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.087262338040098</v>
+        <v>1.117743436123924</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.112006713879097</v>
+        <v>1.166534120297584</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.547985902975725</v>
+        <v>1.629154939139553</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.300421478534652</v>
+        <v>1.382132844948231</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.677705760337034</v>
+        <v>1.783352755554979</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.200546763003054</v>
+        <v>2.33159105540625</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.169102816144282</v>
+        <v>2.323346037490225</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; -0.1382</t>
+          <t>X &gt; -0.1381</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.174256383258751</v>
+        <v>1.123742820927191</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9423806350225021</v>
+        <v>0.9665086980528343</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.5935862617617218</v>
+        <v>0.6187688698117313</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1720872674190517</v>
+        <v>0.1966749901432507</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.001613806277376284</v>
+        <v>0.07541112978010034</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4369188703952176</v>
+        <v>0.4861911288198186</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.179794718025605</v>
+        <v>1.253501920919106</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.356404235158408</v>
+        <v>1.431643401566127</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.479330124612638</v>
+        <v>1.578663432723715</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.916767650121862</v>
+        <v>2.042783333969453</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.758043503355928</v>
+        <v>1.884641046506957</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.252191770653781</v>
+        <v>2.402789384607814</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.705604135731178</v>
+        <v>2.881596499442338</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.747431739980698</v>
+        <v>2.946648721163328</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.1209</t>
+          <t>X &gt; -0.1208</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.5986859595154</v>
+        <v>1.596408832156314</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.728793398789875</v>
+        <v>1.755392025746119</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.383773257815932</v>
+        <v>1.361654037431414</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7677297446878768</v>
+        <v>0.7448979591836604</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.7269526294031365</v>
+        <v>0.7534088978733635</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.7755704401327463</v>
+        <v>0.7773143768714803</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.785387444050656</v>
+        <v>1.811730462857575</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.164089944542525</v>
+        <v>2.192089837864977</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.252361519363028</v>
+        <v>2.30444525262066</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.795477548903811</v>
+        <v>2.874344894802192</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.29226892795706</v>
+        <v>2.371548399481128</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.222169468372087</v>
+        <v>3.325683280200927</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.548287271775095</v>
+        <v>3.677165473099521</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.276510484190673</v>
+        <v>3.42845025547328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; -0.1037</t>
+          <t>X &gt; -0.1036</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1815</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.238092233928455</v>
+        <v>1.208896439575824</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.665473633977584</v>
+        <v>1.664286847532928</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.160509411756969</v>
+        <v>1.160356021752648</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.9601560429486327</v>
+        <v>0.9596615505706296</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.5871557460512946</v>
+        <v>0.6357016658170664</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.9947226131519429</v>
+        <v>1.018680022101556</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.177229884739774</v>
+        <v>2.225241563730094</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.371318265746417</v>
+        <v>2.420565828140134</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.20014327175808</v>
+        <v>2.273400381537776</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.672538525015</v>
+        <v>2.771885850309573</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.24745169182367</v>
+        <v>2.347359727842345</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.108276125170732</v>
+        <v>3.231972746198977</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.459475134116275</v>
+        <v>3.608164681894102</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.024053759549425</v>
+        <v>3.196052519116087</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; -0.08639</t>
+          <t>X &gt; -0.08632</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1593</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.007470661242174</v>
+        <v>1.978274866889542</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.342298378598933</v>
+        <v>2.341111592154277</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.82197771575224</v>
+        <v>1.821824325747919</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.077752137432256</v>
+        <v>2.077257645054253</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.413913306244908</v>
+        <v>1.462459226010679</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.58573805778834</v>
+        <v>1.609695466737953</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.317098006117902</v>
+        <v>2.365109685108223</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.289451835651946</v>
+        <v>2.338699398045662</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.228469679129169</v>
+        <v>2.301726788908866</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.759592941807476</v>
+        <v>2.858940267102049</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.92714539308902</v>
+        <v>2.027053429107696</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.714819213994261</v>
+        <v>2.838515835022505</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.047964029230755</v>
+        <v>3.196653577008583</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.834277206136498</v>
+        <v>3.006275965703161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.06911</t>
+          <t>X &gt; -0.06906</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1379</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.631484259530914</v>
+        <v>2.602288465178283</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.615657122232136</v>
+        <v>2.61447033578748</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.785787840450254</v>
+        <v>1.785634450445933</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.423627197236591</v>
+        <v>2.423132704858588</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.667788695627479</v>
+        <v>1.716334615393251</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.185746057076891</v>
+        <v>3.233757736067211</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.371324258830398</v>
+        <v>3.420571821224115</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.455374734649901</v>
+        <v>3.528631844429597</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.765716997058256</v>
+        <v>3.865064322352829</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.343466890284645</v>
+        <v>3.443374926303321</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.103008204351354</v>
+        <v>4.226704825379599</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.480536828920478</v>
+        <v>4.629226376698306</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.053625633606757</v>
+        <v>4.225624393173419</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.05183</t>
+          <t>X &gt; -0.05179</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.588952965098834</v>
+        <v>3.559757170746202</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.637155518323212</v>
+        <v>3.635968731878556</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.242384133568173</v>
+        <v>3.242230743563852</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.459945521698025</v>
+        <v>3.459451029320022</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3.183664702226785</v>
+        <v>3.232210621992557</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.005056199110776</v>
+        <v>4.029013608060389</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.881044529800938</v>
+        <v>4.929056208791259</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.937993353263117</v>
+        <v>4.987240915656834</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.877011196740341</v>
+        <v>4.950268306520037</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.81311860128384</v>
+        <v>4.912465926578413</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.084399975774744</v>
+        <v>4.184308011793419</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.516158040793819</v>
+        <v>5.639854661822064</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.882033388353769</v>
+        <v>6.030722936131596</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.234406593165453</v>
+        <v>5.406405352732115</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; -0.03456</t>
+          <t>X &gt; -0.03453</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>898</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.866522722249613</v>
+        <v>3.837326927896981</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.482508121390687</v>
+        <v>4.481321334946031</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.53317103507662</v>
+        <v>4.533017645072299</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.220189051716204</v>
+        <v>5.219694559338201</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.68189949862051</v>
+        <v>4.730445418386282</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.647424975917069</v>
+        <v>5.671382384866682</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.453583213532866</v>
+        <v>6.501594892523187</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.986514569746127</v>
+        <v>6.035762132139844</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.925532413223351</v>
+        <v>5.998789523003047</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.077840788385693</v>
+        <v>6.177188113680266</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.316346757074285</v>
+        <v>5.416254793092961</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.132462103193518</v>
+        <v>7.256158724221763</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.603179846762075</v>
+        <v>7.751869394539902</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.940274071598843</v>
+        <v>8.112272831165505</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.01728</t>
+          <t>X &gt; -0.01726</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.435876707740995</v>
+        <v>2.489888175113023</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.001695153255071</v>
+        <v>4.088529271775343</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.665925281359335</v>
+        <v>4.755397344066701</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.098722285764644</v>
+        <v>5.188311688311686</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.01429052389436</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.462950483937924</v>
+        <v>5.577908672239303</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.680811985488702</v>
+        <v>5.82028288604414</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.272744854561267</v>
+        <v>6.415056186266852</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.665620489263908</v>
+        <v>6.832629031675523</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.177275066610292</v>
+        <v>7.372436814496893</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.459714604265386</v>
+        <v>5.653144851809287</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.06595357356472</v>
+        <v>8.135554013416616</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.250946441885205</v>
+        <v>8.346456692913385</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.476682092111737</v>
+        <v>8.595501554928752</v>
       </c>
     </row>
     <row r="35">
@@ -3848,1509 +3848,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.5011</t>
+          <t>X &lt; -0.5007</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.735951439345165</v>
+        <v>1.706755644992533</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.739223177606632</v>
+        <v>3.738036391161977</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.139632515743173</v>
+        <v>2.139479125738852</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.474676936439955</v>
+        <v>3.474182444061952</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.550845214669565</v>
+        <v>6.599391134435336</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.43858069008779</v>
+        <v>4.462538099037403</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.14905105371318</v>
+        <v>3.1970627327035</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.091620964143317</v>
+        <v>5.140868526537034</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.825819530512106</v>
+        <v>3.899076640291803</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.59035856550755</v>
+        <v>6.689705890802124</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.180838130138916</v>
+        <v>5.280746166157591</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.010397005385812</v>
+        <v>4.134093626414057</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.204703983397692</v>
+        <v>7.35339353117552</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.430439633624225</v>
+        <v>7.602438393190887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.4838</t>
+          <t>X &lt; -0.4834</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>5.037057986433773</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.098374066878009</v>
+        <v>1.567088448447727</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.7512217297420207</v>
+        <v>0.2299542337179261</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.738589730473244</v>
+        <v>3.190026954177895</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.057443034520404</v>
+        <v>5.530966492471258</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.402436111774534</v>
+        <v>4.86035578487509</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.412963847746468</v>
+        <v>2.912907242819443</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.803038061102583</v>
+        <v>5.277263161681383</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.29689432612949</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.701660917773751</v>
+        <v>9.133443103805078</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.496959759513558</v>
+        <v>8.929302656268987</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.626576007106976</v>
+        <v>7.100676940803687</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.111187058555473</v>
+        <v>8.592311467070054</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.336922708782005</v>
+        <v>8.841356329085421</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.4665</t>
+          <t>X &lt; -0.4661</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.857112138479735</v>
+        <v>3.739888175113016</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.541700693303234</v>
+        <v>2.156711089957163</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2615213956771569</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.502506564812606</v>
+        <v>5.36507936507936</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.372667715942264</v>
+        <v>5.570274668571884</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.261591041351998</v>
+        <v>4.454171298501926</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.359979273635126</v>
+        <v>1.615737431498687</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.301361334073739</v>
+        <v>2.53879356000423</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.536153825438291</v>
+        <v>3.196265395311883</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.024263198122512</v>
+        <v>7.927992370052451</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.228012744087678</v>
+        <v>9.11274081140526</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.14971484010497</v>
+        <v>7.08757421543681</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.13801469101692</v>
+        <v>8.081305177761884</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.659524989130766</v>
+        <v>7.635905595332794</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.4492</t>
+          <t>X &lt; -0.4489</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>185</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.816381266762946</v>
+        <v>4.787185472410314</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.745735714239657</v>
+        <v>3.744548927795002</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.269883248403538</v>
+        <v>2.269729858399216</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.267224244301609</v>
+        <v>7.315770164067381</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.564598273936696</v>
+        <v>7.588555682886309</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.236644671427285</v>
+        <v>4.284656350417606</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.229035487100006</v>
+        <v>3.278283049493723</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.330215492739399</v>
+        <v>5.403472602519095</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.804621020733862</v>
+        <v>8.903968346028435</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>10.22154148409528</v>
+        <v>10.32144952011396</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.174838555369526</v>
+        <v>9.29853517639777</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>10.37630932367775</v>
+        <v>10.52499887145557</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.520963892823197</v>
+        <v>9.692962652389859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.432</t>
+          <t>X &lt; -0.4316</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>224</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.429798255179939</v>
+        <v>2.400602460827308</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.26504073354468</v>
+        <v>1.263853947100024</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.9154449369246507</v>
+        <v>-0.915598326928972</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.339780206663711</v>
+        <v>2.339285714285708</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.140776367853739</v>
+        <v>3.189322287619511</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.6748686096512273</v>
+        <v>0.722880288641548</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.024342891278373</v>
+        <v>-1.975095328884656</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5932463807702817</v>
+        <v>0.666503490549978</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.421899013011853</v>
+        <v>2.521246338306426</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.556483569037368</v>
+        <v>3.656391605056044</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.805147435678414</v>
+        <v>1.928844056706659</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.724282296650713</v>
+        <v>2.872971844428541</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.396446518305815</v>
+        <v>3.568445277872478</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.4147</t>
+          <t>X &lt; -0.4143</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>266</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.782241864202497</v>
+        <v>2.753046069849866</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3327036273575743</v>
+        <v>-0.3338904138022301</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3515351624885596</v>
+        <v>-0.351688552492881</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.9065095299719914</v>
+        <v>0.9060150375939884</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.368219976876297</v>
+        <v>0.4167658966420689</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.21410524160892</v>
+        <v>-1.190147832659306</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.9228757512510271</v>
+        <v>-0.8748640722607064</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.269643643158069</v>
+        <v>-3.220396080764353</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3231070026883671</v>
+        <v>-0.2498498929086708</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.005731689338127</v>
+        <v>2.105639725356802</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1161995898837986</v>
+        <v>0.2648891376616263</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.3974</t>
+          <t>X &lt; -0.3971</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>301</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3430042352463829</v>
+        <v>0.3138084408937516</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.261537339545022</v>
+        <v>-3.262724125989678</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.991856897057538</v>
+        <v>-2.992010287061859</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.532728098984123</v>
+        <v>-1.533222591362126</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.738791738458552</v>
+        <v>-1.69024581869278</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.099225017793572</v>
+        <v>-4.075267608843959</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.851709463438475</v>
+        <v>-3.803697784448154</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-6.97658541619532</v>
+        <v>-6.927337853801603</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.383082522884209</v>
+        <v>-3.309825413104512</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.907419923865227</v>
+        <v>-1.808072598570654</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4509915140191083</v>
+        <v>-0.351083478000433</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7488392752850501</v>
+        <v>-0.6251426542568055</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.833441955840975</v>
+        <v>-1.684752408063147</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.275480391993192</v>
+        <v>-1.103481632426529</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.3801</t>
+          <t>X &lt; -0.3798</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.069379827453808</v>
+        <v>1.17720380933131</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.316954194604101</v>
+        <v>-2.470870030986795</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.007583567524819</v>
+        <v>-2.8646080193015</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.693926471273734</v>
+        <v>-1.554782975136959</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.232216024369428</v>
+        <v>-2.339017366826347</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.301705900059787</v>
+        <v>-4.426113853907125</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.090558271160269</v>
+        <v>-4.191784692395117</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.628632832106774</v>
+        <v>-6.427528957203243</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.731035106972747</v>
+        <v>-3.514649058965411</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.509947986142848</v>
+        <v>-2.273580884618141</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.9395012154089457</v>
+        <v>-0.7078098277294558</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.496839039384987</v>
+        <v>-1.239613591839493</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.987995809858162</v>
+        <v>-3.699668273565557</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.76226015963163</v>
+        <v>-3.45062341155019</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.3628</t>
+          <t>X &lt; -0.3625</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.299445726571591</v>
+        <v>2.129063432844973</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.637321761841079</v>
+        <v>-1.773701281176855</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.256899348146504</v>
+        <v>-1.136511434440017</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8682762717416068</v>
+        <v>-1.006627393225337</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.889769959204223</v>
+        <v>-0.9804126166514848</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.401181459284899</v>
+        <v>-2.511750809172753</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.485891818551067</v>
+        <v>-2.572406898398214</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.986552193603949</v>
+        <v>-4.069167493833113</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.980350887594433</v>
+        <v>-2.04428443286681</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.02148415420853</v>
+        <v>-1.063989302341582</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.06580435161396991</v>
+        <v>0.02053004393675195</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.191807160113399</v>
+        <v>-1.20996301251278</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.162345610326035</v>
+        <v>-3.151512691653934</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.67821202728296</v>
+        <v>-2.387003912112796</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.3456</t>
+          <t>X &lt; -0.3453</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>443</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.920889838540141</v>
+        <v>1.89169404418751</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.173366231950318</v>
+        <v>-2.174553018394974</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.890936713770834</v>
+        <v>-1.891090103775156</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.083510667247936</v>
+        <v>-1.084005159625939</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1840688541484781</v>
+        <v>0.2326147739142499</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.098692556397019</v>
+        <v>-1.074735147447406</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.183402915663187</v>
+        <v>-1.135391236672866</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.101938828072953</v>
+        <v>-2.052691265679236</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3570519101036282</v>
+        <v>-0.2837948003239319</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3040361691874409</v>
+        <v>-0.2046888438928676</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3941972097984134</v>
+        <v>0.4941052458170887</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.828760980961384</v>
+        <v>-1.705064359933139</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.474645468586303</v>
+        <v>-2.325955920808475</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.24890981835977</v>
+        <v>-2.076911058793108</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.3283</t>
+          <t>X &lt; -0.328</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>494</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9603795160243536</v>
+        <v>0.9311837216717223</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.258094026432182</v>
+        <v>-1.259280812876838</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.652865411187221</v>
+        <v>-1.653018801191543</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3080653688134376</v>
+        <v>-0.3085598611914406</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5706491266738638</v>
+        <v>0.6191950464396356</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9538391918691929</v>
+        <v>-0.9298817829195798</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.848266150325635</v>
+        <v>-1.800254471335315</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.910476494517241</v>
+        <v>-1.861228932123524</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3520254526594471</v>
+        <v>-0.2787683428797507</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.404373398786873</v>
+        <v>-1.3050260734923</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7993579578567847</v>
+        <v>-0.6994499218381094</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.777125554489324</v>
+        <v>-1.653428933461079</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.80456385719544</v>
+        <v>-2.655874309417612</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.376399057171334</v>
+        <v>-2.204400297604671</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.311</t>
+          <t>X &lt; -0.3108</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9704114030939621</v>
+        <v>0.8467786344769763</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.879712743067202</v>
+        <v>-1.796469122056969</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.566519526052339</v>
+        <v>-1.483493329452948</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1973563293666274</v>
+        <v>-0.2935386168601823</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.5032921706350209</v>
+        <v>0.4539613587956808</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.9692453041546685</v>
+        <v>-0.863359129452526</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.115902566075711</v>
+        <v>-1.984085890056086</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.405980059419967</v>
+        <v>-2.273240205209746</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.051033012402918</v>
+        <v>-0.8967852525090905</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.015996056520386</v>
+        <v>-0.8372216071756569</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3357414625681869</v>
+        <v>-0.1579698285633384</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.186319062425255</v>
+        <v>-0.9831953173468548</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.960452216623622</v>
+        <v>-1.731710134370047</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.73471656639709</v>
+        <v>-1.48266527235468</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.2937</t>
+          <t>X &lt; -0.2935</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.09262635410907905</v>
+        <v>-0.04857336334852391</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.857895652103579</v>
+        <v>-1.939442756196684</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.328167807274639</v>
+        <v>-1.410103821434461</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2734434341023046</v>
+        <v>-0.3571428571428612</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.8831822670392953</v>
+        <v>0.8459156942129127</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.1120680177373927</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.831734956274374</v>
+        <v>-1.865031799270547</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.452886804991785</v>
+        <v>-2.484710713500036</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3567040924852733</v>
+        <v>-0.367837168790679</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7443732740231468</v>
+        <v>-0.7301272880672087</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.437674412092619</v>
+        <v>0.4503476490120875</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3179693595172779</v>
+        <v>0.3546682325308268</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7185143135187815</v>
+        <v>-0.6558743094176123</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4317205662917232</v>
+        <v>0.5162474756746818</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.2765</t>
+          <t>X &lt; -0.2762</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3070029870560944</v>
+        <v>-0.1424238026028632</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.777936625701969</v>
+        <v>-1.725600887758716</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.611698192785198</v>
+        <v>-1.562235812006563</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.499705868271171</v>
+        <v>-0.4574214086748967</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.2242766683947082</v>
+        <v>0.3068113445236023</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8808738461497327</v>
+        <v>-0.7381810957333172</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.64861365843133</v>
+        <v>-2.611947366269796</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.115682302218069</v>
+        <v>-2.938310112706134</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.213130096889508</v>
+        <v>-1.022702526584915</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.221534166711656</v>
+        <v>-1.009711023717884</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3042156896282293</v>
+        <v>-0.09809135967796578</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.5503424461088073</v>
+        <v>-0.3188646502070753</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.531503117094026</v>
+        <v>-1.411372646505903</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3240002859418283</v>
+        <v>-0.1860376868615319</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.2592</t>
+          <t>X &lt; -0.259</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7210544128154055</v>
+        <v>0.7098152711033023</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.7669789708888146</v>
+        <v>-0.6303484483174415</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4228340994862307</v>
+        <v>-0.0520329736916878</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.07684917218094967</v>
+        <v>0.5638777989932251</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8932394220409279</v>
+        <v>1.236333062732477</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2872190606392593</v>
+        <v>0.1157966875938143</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.603456513501484</v>
+        <v>-1.097677202647652</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.193677866647832</v>
+        <v>-1.864442093231418</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6536748014957325</v>
+        <v>-0.2470923878992011</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.010982760387172</v>
+        <v>-0.636539113695676</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.1073095344109092</v>
+        <v>0.2075120532353196</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1960840914151945</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9856930728074147</v>
+        <v>-0.619675214394988</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3904992945020709</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.2419</t>
+          <t>X &lt; -0.2417</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.886959617134039</v>
+        <v>0.9257856110104541</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5169725899194262</v>
+        <v>-0.4522632690171946</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.124525455377352</v>
+        <v>0.2822038708732322</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.083766143007161</v>
+        <v>1.289674391317092</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.892626848978828</v>
+        <v>1.988140376005937</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6355967335361896</v>
+        <v>0.8790684178434844</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.07087528376106178</v>
+        <v>0.154614877430717</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5379439275478006</v>
+        <v>-0.2547345041423839</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7482241749967784</v>
+        <v>1.003282939171527</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4164400936928274</v>
+        <v>0.6506737290974485</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.55888919449999</v>
+        <v>1.746028183575767</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.593267346855313</v>
+        <v>1.760624595008927</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6549817785159959</v>
+        <v>0.8478683247598084</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.398852143768437</v>
+        <v>1.510991861723411</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.2246</t>
+          <t>X &lt; -0.2244</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1112</v>
+        <v>1117</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.02355624137978651</v>
+        <v>0.1028199731643937</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.824420834430768</v>
+        <v>-0.8131470660712097</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4134625862404206</v>
+        <v>-0.3610286729804386</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6612727821885471</v>
+        <v>0.7050241055569586</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.287857781064176</v>
+        <v>1.242496890794108</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.110956291146735</v>
+        <v>0.1416960118273494</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1041772995562624</v>
+        <v>-0.1373792203267854</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5712459433430013</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.6245043956458929</v>
+        <v>0.6167233197840787</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.2254144006839667</v>
+        <v>-0.2466108045507198</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7368503297452378</v>
+        <v>0.7607896645479357</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.7712284821005611</v>
+        <v>0.7804285187562243</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.04694411844362634</v>
+        <v>-0.1009538493942017</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5894064360858806</v>
+        <v>0.4166675569363036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.2073</t>
+          <t>X &lt; -0.2072</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1300</v>
+        <v>1309</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2671755725190863</v>
+        <v>-0.1651799035556678</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.08140693643240127</v>
+        <v>-0.0433267601563827</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.2055279426039789</v>
+        <v>-0.1688450801757213</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5783172052427972</v>
+        <v>0.5329253763673734</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5415092490613489</v>
+        <v>0.4646853918900504</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2683364949162979</v>
+        <v>0.2479576816960503</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1577343701910223</v>
+        <v>-0.2269677356745632</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.04573583064905762</v>
+        <v>-0.1191067357287707</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6607417211934745</v>
+        <v>0.5706946190561695</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.189177075136385</v>
+        <v>-0.2868675774807627</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6805653583148654</v>
+        <v>0.6184996189933329</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4514607997337095</v>
+        <v>0.3385912507787836</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2286058938836106</v>
+        <v>0.06285734061174253</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3442487161080194</v>
+        <v>0.1259319088885178</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.1901</t>
+          <t>X &lt; -0.1899</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1469</v>
+        <v>1480</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6590536823562161</v>
+        <v>-0.6012035864409029</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.884809753577926</v>
+        <v>-0.8761307330991386</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.8382248597045745</v>
+        <v>-0.8317619754869838</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1984333546228711</v>
+        <v>-0.1960690316395031</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3617850085236043</v>
+        <v>-0.4474665447704069</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.501423062226813</v>
+        <v>-0.5413484147597245</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8882363071122299</v>
+        <v>-0.9691650567326491</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6408683150071894</v>
+        <v>-0.7259365132722735</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2578148714103676</v>
+        <v>-0.3895931905467052</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8667611557399724</v>
+        <v>-1.041759052529159</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1508145676085988</v>
+        <v>-0.3322655570670676</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.4181943143458753</v>
+        <v>-0.6412831844732167</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.004459199947931</v>
+        <v>-1.269077446591034</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9450637413460328</v>
+        <v>-1.252983293556085</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.1728</t>
+          <t>X &lt; -0.1726</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1598</v>
+        <v>1609</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.518780710857136</v>
+        <v>-1.462023045602159</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.731853676393207</v>
+        <v>-1.718211797149564</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.845481339304122</v>
+        <v>-1.832705910703218</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.060628464267346</v>
+        <v>-1.052633900997094</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8190200584952763</v>
+        <v>-0.8908913800478118</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.9861068521108933</v>
+        <v>-1.017638637593727</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.473551506058612</v>
+        <v>-1.540203162560715</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.284006232924263</v>
+        <v>-1.353965297924908</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.9370873684499301</v>
+        <v>-1.047848607166429</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.503439849124767</v>
+        <v>-1.652155043324967</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9245327600426663</v>
+        <v>-1.078188331136793</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9805668500358777</v>
+        <v>-1.172047137759961</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.428703944750168</v>
+        <v>-1.657307658677055</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.230989562509492</v>
+        <v>-1.49847738926772</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; -0.1555</t>
+          <t>X &lt; -0.1554</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1757</v>
+        <v>1769</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.068486652003273</v>
+        <v>-1.051077032518855</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.406969280183816</v>
+        <v>-1.37009969050326</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.545697037764981</v>
+        <v>-1.509498808469907</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6498006001921368</v>
+        <v>-0.6190877700152626</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5348020175208106</v>
+        <v>-0.5719263063062456</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8865157295852342</v>
+        <v>-0.8876188596922887</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.450981730484834</v>
+        <v>-1.481109415348158</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.434084808464981</v>
+        <v>-1.466292511983248</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.294320507506036</v>
+        <v>-1.360292289768914</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.943264854920336</v>
+        <v>-2.040986761363229</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.549035911482115</v>
+        <v>-1.650364280142277</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.938355366238262</v>
+        <v>-2.069603148262289</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.441388920641664</v>
+        <v>-2.603723070825694</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.355545513566696</v>
+        <v>-2.550326425268921</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; -0.1382</t>
+          <t>X &lt; -0.1381</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1915</v>
+        <v>1927</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.236102752526058</v>
+        <v>-1.169905639319978</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.9525068978586901</v>
+        <v>-0.9731238765203969</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7485557513438721</v>
+        <v>-0.7718566197197703</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.01898602710252106</v>
+        <v>-0.0463529758831811</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1986171756945367</v>
+        <v>0.1122856878556249</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3073922813611887</v>
+        <v>-0.3617201743662903</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.248351250613389</v>
+        <v>-1.325058845647121</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.531435551351258</v>
+        <v>-1.608113952785324</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.512408381134485</v>
+        <v>-1.617399200961408</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.073792567424391</v>
+        <v>-2.206365187919815</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.833245315217063</v>
+        <v>-1.968145774662688</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.292121362294615</v>
+        <v>-2.452126838649939</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.631928559299183</v>
+        <v>-2.819455541463576</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.639081269832936</v>
+        <v>-2.853917388003424</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.1209</t>
+          <t>X &lt; -0.1208</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2080</v>
+        <v>2092</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.45368239460506</v>
+        <v>-1.441228214435675</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.558641320538911</v>
+        <v>-1.574277503198729</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.40222501480946</v>
+        <v>-1.372428705300003</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5767440585447616</v>
+        <v>-0.5512437134701642</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5148517522310598</v>
+        <v>-0.5389193660148166</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5745753824783364</v>
+        <v>-0.5736064792758526</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.639629302594656</v>
+        <v>-1.656654183556107</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.081270024547784</v>
+        <v>-2.09723546234509</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.020876606554147</v>
+        <v>-2.061245334301852</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.605349410349824</v>
+        <v>-2.668911786012011</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.064272894853993</v>
+        <v>-2.13162407854437</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.868415072898507</v>
+        <v>-2.955007764824245</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.022654272306518</v>
+        <v>-3.13365739589635</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.723058976199681</v>
+        <v>-2.859101840401216</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; -0.1037</t>
+          <t>X &lt; -0.1036</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2275</v>
+        <v>2286</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9074894571077792</v>
+        <v>-0.8789678492454058</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.228088131468759</v>
+        <v>-1.221226246857455</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.9873109536725551</v>
+        <v>-0.9824557185578016</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6148540540427589</v>
+        <v>-0.6114982578397274</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2977400194367306</v>
+        <v>-0.3365880765261551</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6334815404374652</v>
+        <v>-0.6503283624493505</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.65861079438033</v>
+        <v>-1.690520745561933</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.883231536609365</v>
+        <v>-1.915104054888147</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.613833819730971</v>
+        <v>-1.666967545179894</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.045325020085379</v>
+        <v>-2.118101759011104</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.655638593260377</v>
+        <v>-1.730786201846534</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.256038962464508</v>
+        <v>-2.348128970266373</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.388854785950336</v>
+        <v>-2.501153647482255</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.007399635540331</v>
+        <v>-2.140997291806315</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; -0.08639</t>
+          <t>X &lt; -0.08632</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2497</v>
+        <v>2508</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.206015632127979</v>
+        <v>-1.181274062094438</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.401787257117512</v>
+        <v>-1.394876211630134</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.217336028289417</v>
+        <v>-1.211917728051866</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.185527503177305</v>
+        <v>-1.180018154998301</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7448980136307028</v>
+        <v>-0.7740836945588256</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.8650289580857446</v>
+        <v>-0.8772630770500953</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.407513864105056</v>
+        <v>-1.433467339873083</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.453777569664318</v>
+        <v>-1.480365814167072</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.293458541006579</v>
+        <v>-1.33682917956542</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.681995143611218</v>
+        <v>-1.741151295906498</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.104945002391204</v>
+        <v>-1.1670282049229</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.528686097734955</v>
+        <v>-1.604878197135115</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.606682475166743</v>
+        <v>-1.699317912446709</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.438998873306979</v>
+        <v>-1.548039114927704</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.06911</t>
+          <t>X &lt; -0.06906</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2711</v>
+        <v>2722</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.269462286040955</v>
+        <v>-1.24868586510636</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.245976526829914</v>
+        <v>-1.240326218016499</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.9600549925560173</v>
+        <v>-0.9561084936740372</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.104167659141929</v>
+        <v>-1.099456180715329</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.7037614472723206</v>
+        <v>-0.7270218040266769</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.158799636662387</v>
+        <v>-1.167013072682444</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.554974762576251</v>
+        <v>-1.57453373009897</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.708047344719667</v>
+        <v>-1.727661311289353</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.671721403367982</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.842932610245185</v>
+        <v>-1.888996298733716</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.585505061344776</v>
+        <v>-1.632926874629405</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.899567955822832</v>
+        <v>-1.958558922106015</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.967826847892063</v>
+        <v>-2.040037703863781</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.72192045223747</v>
+        <v>-1.807722455936691</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.05183</t>
+          <t>X &lt; -0.05179</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2945</v>
+        <v>2956</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.33149074317803</v>
+        <v>-1.314423040784597</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.335930327859252</v>
+        <v>-1.330485675541496</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.306900571952674</v>
+        <v>-1.301991509075442</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.226360716710715</v>
+        <v>-1.221606781620267</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.103468723547763</v>
+        <v>-1.119579181905905</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.431292300010092</v>
+        <v>-1.435954657413497</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.836745792207083</v>
+        <v>-1.849922372753767</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.913151769624697</v>
+        <v>-1.926563931180404</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.786596234241827</v>
+        <v>-1.810489079527699</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.804563952642368</v>
+        <v>-1.839274897214814</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.482041338890518</v>
+        <v>-1.51819681767364</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.971998814745753</v>
+        <v>-2.016268471063078</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.000344315705021</v>
+        <v>-2.054953417661416</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.722095805244997</v>
+        <v>-1.787489382865971</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; -0.03456</t>
+          <t>X &lt; -0.03453</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3192</v>
+        <v>3203</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.030057996212975</v>
+        <v>-1.017574511454143</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.189480400751741</v>
+        <v>-1.185046297290114</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.317969355996055</v>
+        <v>-1.313411465874651</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.358522193621823</v>
+        <v>-1.353719265483981</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.192969782902729</v>
+        <v>-1.203801711668874</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.472563888225466</v>
+        <v>-1.474883340066881</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.759485876125588</v>
+        <v>-1.768218954794143</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.678423566700516</v>
+        <v>-1.687817360670259</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.566283759092983</v>
+        <v>-1.583451977921698</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.648479138248661</v>
+        <v>-1.67340041656017</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.397965346679158</v>
+        <v>-1.423926548406214</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.847348315283213</v>
+        <v>-1.879101118243199</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.874645044407856</v>
+        <v>-1.914013174298056</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.945032178436037</v>
+        <v>-1.991353571420596</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.01728</t>
+          <t>X &lt; -0.01726</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3429</v>
+        <v>3441</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.4181618178673006</v>
+        <v>-0.4255721607294802</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.7064584153738309</v>
+        <v>-0.7194111226116107</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.9403618804462397</v>
+        <v>-0.9528438160863928</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.8818010254220212</v>
+        <v>-0.8943784410315843</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.8518896339745794</v>
+        <v>-0.8753775053411559</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.9461236787404559</v>
+        <v>-0.9638645250862368</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.0443231415545</v>
+        <v>-1.06697718567068</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.204655846154644</v>
+        <v>-1.227162343680128</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.191687889967724</v>
+        <v>-1.219482331521156</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.326774575269951</v>
+        <v>-1.360025691550518</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.9619146993609036</v>
+        <v>-0.9966281394271093</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.406900280522613</v>
+        <v>-1.416193493602456</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.3445952543697</v>
+        <v>-1.359669062021197</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.365197859480297</v>
+        <v>-1.385212296752833</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3733</v>
+        <v>3744</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1851338628888612</v>
+        <v>-0.1811259318872516</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3671355014352997</v>
+        <v>-0.365919367976808</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.4804632519429646</v>
+        <v>-0.4790375508209195</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.4693921531698777</v>
+        <v>-0.4679579876703031</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4320838291379374</v>
+        <v>-0.4365865091526047</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4943829205697625</v>
+        <v>-0.4957813193611358</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4041993811814777</v>
+        <v>-0.4087227124629251</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6160452181037286</v>
+        <v>-0.6200953288846591</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4216680119531091</v>
+        <v>-0.4291458254581073</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.6949775877756466</v>
+        <v>-0.7047599126464732</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3762940387937732</v>
+        <v>-0.3870812684808769</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.6214637710532784</v>
+        <v>-0.6343662247364037</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.5446652127226059</v>
+        <v>-0.5607731488958834</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.6253570866078846</v>
+        <v>-0.644008934581727</v>
       </c>
     </row>
   </sheetData>
